--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -541,6 +541,12 @@
     <t>['38', '64', '90+4']</t>
   </si>
   <si>
+    <t>['46', '62', '66']</t>
+  </si>
+  <si>
+    <t>['16', '23']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -755,6 +761,9 @@
   </si>
   <si>
     <t>['45', '90+4']</t>
+  </si>
+  <si>
+    <t>['14', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1372,7 +1381,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1862,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4">
         <v>0.64</v>
@@ -1990,7 +1999,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2071,7 +2080,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2402,7 +2411,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2608,7 +2617,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2814,7 +2823,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3101,7 +3110,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ10">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3226,7 +3235,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3432,7 +3441,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3638,7 +3647,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3925,7 +3934,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ14">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -4334,10 +4343,10 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.8</v>
@@ -4749,7 +4758,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ18">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR18">
         <v>2.13</v>
@@ -5158,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.42</v>
@@ -5286,7 +5295,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5492,7 +5501,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5779,7 +5788,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ23">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR23">
         <v>2.19</v>
@@ -6110,7 +6119,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6316,7 +6325,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6522,7 +6531,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6603,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>2.02</v>
@@ -6728,7 +6737,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6806,7 +6815,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28">
         <v>1.36</v>
@@ -7012,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ29">
         <v>1.45</v>
@@ -7140,7 +7149,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7346,7 +7355,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7424,7 +7433,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ31">
         <v>1.18</v>
@@ -7552,7 +7561,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7964,7 +7973,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8454,7 +8463,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8663,7 +8672,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR37">
         <v>1.26</v>
@@ -8788,7 +8797,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9278,7 +9287,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ40">
         <v>0.25</v>
@@ -9406,7 +9415,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9487,7 +9496,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ41">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR41">
         <v>1.54</v>
@@ -9612,7 +9621,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9690,7 +9699,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
         <v>1.18</v>
@@ -10102,10 +10111,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ44">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR44">
         <v>1.71</v>
@@ -10308,7 +10317,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ45">
         <v>0.25</v>
@@ -10436,7 +10445,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10514,7 +10523,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46">
         <v>1.5</v>
@@ -10642,7 +10651,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10929,7 +10938,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ48">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -11341,7 +11350,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ50">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR50">
         <v>1.68</v>
@@ -11672,7 +11681,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11878,7 +11887,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12084,7 +12093,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12162,7 +12171,7 @@
         <v>2.6</v>
       </c>
       <c r="AP54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
         <v>1.92</v>
@@ -12290,7 +12299,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12702,7 +12711,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12908,7 +12917,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13114,7 +13123,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13192,10 +13201,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR59">
         <v>1.49</v>
@@ -13320,7 +13329,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13401,7 +13410,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR60">
         <v>1.61</v>
@@ -13810,7 +13819,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62">
         <v>1.36</v>
@@ -14350,7 +14359,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14556,7 +14565,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14637,7 +14646,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14843,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR67">
         <v>2.01</v>
@@ -14968,7 +14977,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15049,7 +15058,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ68">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR68">
         <v>1.47</v>
@@ -15380,7 +15389,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15664,7 +15673,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ71">
         <v>1.5</v>
@@ -15998,7 +16007,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16204,7 +16213,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16410,7 +16419,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16488,7 +16497,7 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
         <v>0.25</v>
@@ -16822,7 +16831,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17234,7 +17243,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17440,7 +17449,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17646,7 +17655,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17724,10 +17733,10 @@
         <v>2.4</v>
       </c>
       <c r="AP81">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ81">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR81">
         <v>1.49</v>
@@ -17933,7 +17942,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ82">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18058,7 +18067,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18264,7 +18273,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18342,10 +18351,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR84">
         <v>1.76</v>
@@ -18676,7 +18685,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18960,7 +18969,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
         <v>1.92</v>
@@ -19169,7 +19178,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ88">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR88">
         <v>1.52</v>
@@ -19294,7 +19303,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19500,7 +19509,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19706,7 +19715,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20118,7 +20127,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20196,7 +20205,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20324,7 +20333,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20402,10 +20411,10 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20530,7 +20539,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20736,7 +20745,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20817,7 +20826,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR96">
         <v>1.86</v>
@@ -20942,7 +20951,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21020,7 +21029,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ97">
         <v>1.42</v>
@@ -21148,7 +21157,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21229,7 +21238,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ98">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.5</v>
@@ -21354,7 +21363,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21432,7 +21441,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21560,7 +21569,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21766,7 +21775,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21972,7 +21981,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22053,7 +22062,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ102">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR102">
         <v>1.66</v>
@@ -22178,7 +22187,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22256,7 +22265,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ103">
         <v>0.64</v>
@@ -22384,7 +22393,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22796,7 +22805,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22877,7 +22886,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -23002,7 +23011,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23080,7 +23089,7 @@
         <v>1.44</v>
       </c>
       <c r="AP107">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ107">
         <v>1.42</v>
@@ -23286,7 +23295,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ108">
         <v>1.18</v>
@@ -23414,7 +23423,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23492,10 +23501,10 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.77</v>
@@ -23826,7 +23835,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -24032,7 +24041,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24238,7 +24247,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25062,7 +25071,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25143,7 +25152,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ117">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25268,7 +25277,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25552,10 +25561,10 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.75</v>
@@ -25680,7 +25689,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25758,7 +25767,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ120">
         <v>1.92</v>
@@ -25886,7 +25895,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -25964,10 +25973,10 @@
         <v>2.44</v>
       </c>
       <c r="AP121">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ121">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR121">
         <v>1.78</v>
@@ -26092,7 +26101,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26173,7 +26182,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ122">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26298,7 +26307,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26376,7 +26385,7 @@
         <v>1.3</v>
       </c>
       <c r="AP123">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -26504,7 +26513,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26710,7 +26719,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26916,7 +26925,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27200,7 +27209,7 @@
         <v>1.6</v>
       </c>
       <c r="AP127">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127">
         <v>1.45</v>
@@ -27328,7 +27337,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q128">
         <v>3.55</v>
@@ -27534,7 +27543,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q129">
         <v>3.1</v>
@@ -27740,7 +27749,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q130">
         <v>3.55</v>
@@ -27821,7 +27830,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ130">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AR130">
         <v>1.69</v>
@@ -28027,7 +28036,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ131">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28564,7 +28573,7 @@
         <v>171</v>
       </c>
       <c r="P134" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28770,7 +28779,7 @@
         <v>172</v>
       </c>
       <c r="P135" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -28848,7 +28857,7 @@
         <v>1.55</v>
       </c>
       <c r="AP135">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ135">
         <v>1.5</v>
@@ -29182,7 +29191,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29388,7 +29397,7 @@
         <v>139</v>
       </c>
       <c r="P138" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q138">
         <v>2.3</v>
@@ -29545,6 +29554,624 @@
       </c>
       <c r="BP138">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7806896</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F139">
+        <v>24</v>
+      </c>
+      <c r="G139" t="s">
+        <v>81</v>
+      </c>
+      <c r="H139" t="s">
+        <v>71</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>3</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>4</v>
+      </c>
+      <c r="O139" t="s">
+        <v>175</v>
+      </c>
+      <c r="P139" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q139">
+        <v>2.5</v>
+      </c>
+      <c r="R139">
+        <v>2.15</v>
+      </c>
+      <c r="S139">
+        <v>3.9</v>
+      </c>
+      <c r="T139">
+        <v>1.36</v>
+      </c>
+      <c r="U139">
+        <v>2.87</v>
+      </c>
+      <c r="V139">
+        <v>2.65</v>
+      </c>
+      <c r="W139">
+        <v>1.42</v>
+      </c>
+      <c r="X139">
+        <v>6.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.09</v>
+      </c>
+      <c r="Z139">
+        <v>1.83</v>
+      </c>
+      <c r="AA139">
+        <v>3.39</v>
+      </c>
+      <c r="AB139">
+        <v>3.58</v>
+      </c>
+      <c r="AC139">
+        <v>1.05</v>
+      </c>
+      <c r="AD139">
+        <v>9</v>
+      </c>
+      <c r="AE139">
+        <v>1.28</v>
+      </c>
+      <c r="AF139">
+        <v>3.6</v>
+      </c>
+      <c r="AG139">
+        <v>1.77</v>
+      </c>
+      <c r="AH139">
+        <v>1.93</v>
+      </c>
+      <c r="AI139">
+        <v>1.68</v>
+      </c>
+      <c r="AJ139">
+        <v>2</v>
+      </c>
+      <c r="AK139">
+        <v>1.27</v>
+      </c>
+      <c r="AL139">
+        <v>1.28</v>
+      </c>
+      <c r="AM139">
+        <v>1.8</v>
+      </c>
+      <c r="AN139">
+        <v>1.64</v>
+      </c>
+      <c r="AO139">
+        <v>0.91</v>
+      </c>
+      <c r="AP139">
+        <v>1.75</v>
+      </c>
+      <c r="AQ139">
+        <v>0.83</v>
+      </c>
+      <c r="AR139">
+        <v>1.78</v>
+      </c>
+      <c r="AS139">
+        <v>1.62</v>
+      </c>
+      <c r="AT139">
+        <v>3.4</v>
+      </c>
+      <c r="AU139">
+        <v>9</v>
+      </c>
+      <c r="AV139">
+        <v>3</v>
+      </c>
+      <c r="AW139">
+        <v>11</v>
+      </c>
+      <c r="AX139">
+        <v>7</v>
+      </c>
+      <c r="AY139">
+        <v>20</v>
+      </c>
+      <c r="AZ139">
+        <v>10</v>
+      </c>
+      <c r="BA139">
+        <v>5</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>8</v>
+      </c>
+      <c r="BD139">
+        <v>0</v>
+      </c>
+      <c r="BE139">
+        <v>0</v>
+      </c>
+      <c r="BF139">
+        <v>0</v>
+      </c>
+      <c r="BG139">
+        <v>0</v>
+      </c>
+      <c r="BH139">
+        <v>0</v>
+      </c>
+      <c r="BI139">
+        <v>0</v>
+      </c>
+      <c r="BJ139">
+        <v>0</v>
+      </c>
+      <c r="BK139">
+        <v>0</v>
+      </c>
+      <c r="BL139">
+        <v>0</v>
+      </c>
+      <c r="BM139">
+        <v>0</v>
+      </c>
+      <c r="BN139">
+        <v>0</v>
+      </c>
+      <c r="BO139">
+        <v>0</v>
+      </c>
+      <c r="BP139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7806897</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F140">
+        <v>24</v>
+      </c>
+      <c r="G140" t="s">
+        <v>79</v>
+      </c>
+      <c r="H140" t="s">
+        <v>80</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>3</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>176</v>
+      </c>
+      <c r="P140" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q140">
+        <v>2.75</v>
+      </c>
+      <c r="R140">
+        <v>2.05</v>
+      </c>
+      <c r="S140">
+        <v>3.6</v>
+      </c>
+      <c r="T140">
+        <v>1.4</v>
+      </c>
+      <c r="U140">
+        <v>2.75</v>
+      </c>
+      <c r="V140">
+        <v>2.75</v>
+      </c>
+      <c r="W140">
+        <v>1.39</v>
+      </c>
+      <c r="X140">
+        <v>7</v>
+      </c>
+      <c r="Y140">
+        <v>1.08</v>
+      </c>
+      <c r="Z140">
+        <v>2.09</v>
+      </c>
+      <c r="AA140">
+        <v>3.17</v>
+      </c>
+      <c r="AB140">
+        <v>3.07</v>
+      </c>
+      <c r="AC140">
+        <v>1.06</v>
+      </c>
+      <c r="AD140">
+        <v>8.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.31</v>
+      </c>
+      <c r="AF140">
+        <v>3.44</v>
+      </c>
+      <c r="AG140">
+        <v>1.93</v>
+      </c>
+      <c r="AH140">
+        <v>1.77</v>
+      </c>
+      <c r="AI140">
+        <v>1.75</v>
+      </c>
+      <c r="AJ140">
+        <v>1.93</v>
+      </c>
+      <c r="AK140">
+        <v>1.33</v>
+      </c>
+      <c r="AL140">
+        <v>1.31</v>
+      </c>
+      <c r="AM140">
+        <v>1.65</v>
+      </c>
+      <c r="AN140">
+        <v>1.36</v>
+      </c>
+      <c r="AO140">
+        <v>1.09</v>
+      </c>
+      <c r="AP140">
+        <v>1.5</v>
+      </c>
+      <c r="AQ140">
+        <v>1</v>
+      </c>
+      <c r="AR140">
+        <v>1.78</v>
+      </c>
+      <c r="AS140">
+        <v>1.37</v>
+      </c>
+      <c r="AT140">
+        <v>3.15</v>
+      </c>
+      <c r="AU140">
+        <v>9</v>
+      </c>
+      <c r="AV140">
+        <v>6</v>
+      </c>
+      <c r="AW140">
+        <v>7</v>
+      </c>
+      <c r="AX140">
+        <v>12</v>
+      </c>
+      <c r="AY140">
+        <v>16</v>
+      </c>
+      <c r="AZ140">
+        <v>18</v>
+      </c>
+      <c r="BA140">
+        <v>6</v>
+      </c>
+      <c r="BB140">
+        <v>3</v>
+      </c>
+      <c r="BC140">
+        <v>9</v>
+      </c>
+      <c r="BD140">
+        <v>1.87</v>
+      </c>
+      <c r="BE140">
+        <v>8</v>
+      </c>
+      <c r="BF140">
+        <v>2.38</v>
+      </c>
+      <c r="BG140">
+        <v>1.5</v>
+      </c>
+      <c r="BH140">
+        <v>2.38</v>
+      </c>
+      <c r="BI140">
+        <v>1.83</v>
+      </c>
+      <c r="BJ140">
+        <v>1.85</v>
+      </c>
+      <c r="BK140">
+        <v>2.33</v>
+      </c>
+      <c r="BL140">
+        <v>1.52</v>
+      </c>
+      <c r="BM140">
+        <v>3.05</v>
+      </c>
+      <c r="BN140">
+        <v>1.32</v>
+      </c>
+      <c r="BO140">
+        <v>4.1</v>
+      </c>
+      <c r="BP140">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7806898</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45864.29166666666</v>
+      </c>
+      <c r="F141">
+        <v>24</v>
+      </c>
+      <c r="G141" t="s">
+        <v>72</v>
+      </c>
+      <c r="H141" t="s">
+        <v>74</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>2</v>
+      </c>
+      <c r="N141">
+        <v>3</v>
+      </c>
+      <c r="O141" t="s">
+        <v>105</v>
+      </c>
+      <c r="P141" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q141">
+        <v>3.4</v>
+      </c>
+      <c r="R141">
+        <v>2</v>
+      </c>
+      <c r="S141">
+        <v>3</v>
+      </c>
+      <c r="T141">
+        <v>1.44</v>
+      </c>
+      <c r="U141">
+        <v>2.55</v>
+      </c>
+      <c r="V141">
+        <v>3</v>
+      </c>
+      <c r="W141">
+        <v>1.33</v>
+      </c>
+      <c r="X141">
+        <v>8.25</v>
+      </c>
+      <c r="Y141">
+        <v>1.06</v>
+      </c>
+      <c r="Z141">
+        <v>2.67</v>
+      </c>
+      <c r="AA141">
+        <v>3.1</v>
+      </c>
+      <c r="AB141">
+        <v>2.37</v>
+      </c>
+      <c r="AC141">
+        <v>1.03</v>
+      </c>
+      <c r="AD141">
+        <v>7.6</v>
+      </c>
+      <c r="AE141">
+        <v>1.32</v>
+      </c>
+      <c r="AF141">
+        <v>2.97</v>
+      </c>
+      <c r="AG141">
+        <v>1.85</v>
+      </c>
+      <c r="AH141">
+        <v>1.85</v>
+      </c>
+      <c r="AI141">
+        <v>1.87</v>
+      </c>
+      <c r="AJ141">
+        <v>1.82</v>
+      </c>
+      <c r="AK141">
+        <v>1.55</v>
+      </c>
+      <c r="AL141">
+        <v>1.32</v>
+      </c>
+      <c r="AM141">
+        <v>1.4</v>
+      </c>
+      <c r="AN141">
+        <v>1.33</v>
+      </c>
+      <c r="AO141">
+        <v>2.55</v>
+      </c>
+      <c r="AP141">
+        <v>1.23</v>
+      </c>
+      <c r="AQ141">
+        <v>2.58</v>
+      </c>
+      <c r="AR141">
+        <v>1.49</v>
+      </c>
+      <c r="AS141">
+        <v>1.4</v>
+      </c>
+      <c r="AT141">
+        <v>2.89</v>
+      </c>
+      <c r="AU141">
+        <v>3</v>
+      </c>
+      <c r="AV141">
+        <v>4</v>
+      </c>
+      <c r="AW141">
+        <v>7</v>
+      </c>
+      <c r="AX141">
+        <v>2</v>
+      </c>
+      <c r="AY141">
+        <v>10</v>
+      </c>
+      <c r="AZ141">
+        <v>6</v>
+      </c>
+      <c r="BA141">
+        <v>6</v>
+      </c>
+      <c r="BB141">
+        <v>1</v>
+      </c>
+      <c r="BC141">
+        <v>7</v>
+      </c>
+      <c r="BD141">
+        <v>0</v>
+      </c>
+      <c r="BE141">
+        <v>0</v>
+      </c>
+      <c r="BF141">
+        <v>0</v>
+      </c>
+      <c r="BG141">
+        <v>0</v>
+      </c>
+      <c r="BH141">
+        <v>0</v>
+      </c>
+      <c r="BI141">
+        <v>0</v>
+      </c>
+      <c r="BJ141">
+        <v>0</v>
+      </c>
+      <c r="BK141">
+        <v>0</v>
+      </c>
+      <c r="BL141">
+        <v>0</v>
+      </c>
+      <c r="BM141">
+        <v>0</v>
+      </c>
+      <c r="BN141">
+        <v>0</v>
+      </c>
+      <c r="BO141">
+        <v>0</v>
+      </c>
+      <c r="BP141">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="253">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,9 @@
     <t>['16', '23']</t>
   </si>
   <si>
+    <t>['51', '90+7']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -764,6 +767,12 @@
   </si>
   <si>
     <t>['14', '90+4']</t>
+  </si>
+  <si>
+    <t>['30', '83']</t>
+  </si>
+  <si>
+    <t>['68']</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1381,7 +1390,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1668,7 +1677,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ3">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1999,7 +2008,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2411,7 +2420,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2489,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2617,7 +2626,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2823,7 +2832,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2901,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ9">
         <v>0.64</v>
@@ -3235,7 +3244,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3313,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3441,7 +3450,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3647,7 +3656,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3725,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4549,7 +4558,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
         <v>0.64</v>
@@ -4755,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18">
         <v>0.83</v>
@@ -5170,7 +5179,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5295,7 +5304,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5373,7 +5382,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21">
         <v>1.92</v>
@@ -5501,7 +5510,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -6119,7 +6128,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6325,7 +6334,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6403,10 +6412,10 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR26">
         <v>1.64</v>
@@ -6531,7 +6540,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6609,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6737,7 +6746,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6818,7 +6827,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7149,7 +7158,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7230,7 +7239,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ30">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7355,7 +7364,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7436,7 +7445,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>1.73</v>
@@ -7561,7 +7570,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7848,7 +7857,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>1.88</v>
@@ -7973,7 +7982,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8051,7 +8060,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>1.45</v>
@@ -8797,7 +8806,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9084,7 +9093,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR39">
         <v>2.14</v>
@@ -9415,7 +9424,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9493,7 +9502,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41">
         <v>2.58</v>
@@ -9621,7 +9630,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9702,7 +9711,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -10445,7 +10454,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10651,7 +10660,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11141,7 +11150,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
         <v>1.45</v>
@@ -11553,10 +11562,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>2.12</v>
@@ -11681,7 +11690,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11887,7 +11896,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12093,7 +12102,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12299,7 +12308,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12586,7 +12595,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ56">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12711,7 +12720,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12917,7 +12926,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -12998,7 +13007,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13123,7 +13132,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13329,7 +13338,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13616,7 +13625,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ61">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR61">
         <v>1.8</v>
@@ -13822,7 +13831,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -14025,7 +14034,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -14359,7 +14368,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14565,7 +14574,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14643,7 +14652,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -14849,7 +14858,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ67">
         <v>0.83</v>
@@ -14977,7 +14986,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15261,7 +15270,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
         <v>0.64</v>
@@ -15389,7 +15398,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15470,7 +15479,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ70">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>2.06</v>
@@ -16007,7 +16016,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16213,7 +16222,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16294,7 +16303,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ74">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR74">
         <v>1.59</v>
@@ -16419,7 +16428,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16831,7 +16840,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17115,10 +17124,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17243,7 +17252,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17324,7 +17333,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ79">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.5</v>
@@ -17449,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17527,7 +17536,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -17655,7 +17664,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -18067,7 +18076,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18145,10 +18154,10 @@
         <v>1.86</v>
       </c>
       <c r="AP83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.46</v>
@@ -18273,7 +18282,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18685,7 +18694,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18763,10 +18772,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ86">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -19303,7 +19312,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19384,7 +19393,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ89">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.57</v>
@@ -19509,7 +19518,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19715,7 +19724,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19999,7 +20008,7 @@
         <v>0.29</v>
       </c>
       <c r="AP92">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92">
         <v>0.25</v>
@@ -20127,7 +20136,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20333,7 +20342,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20539,7 +20548,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20617,10 +20626,10 @@
         <v>1.29</v>
       </c>
       <c r="AP95">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
         <v>1.37</v>
@@ -20745,7 +20754,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20823,7 +20832,7 @@
         <v>2.29</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ96">
         <v>2.58</v>
@@ -20951,7 +20960,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21032,7 +21041,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ97">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR97">
         <v>1.74</v>
@@ -21157,7 +21166,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21235,7 +21244,7 @@
         <v>0.86</v>
       </c>
       <c r="AP98">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ98">
         <v>1</v>
@@ -21363,7 +21372,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21444,7 +21453,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ99">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.53</v>
@@ -21569,7 +21578,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21775,7 +21784,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21856,7 +21865,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -21981,7 +21990,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22187,7 +22196,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22393,7 +22402,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22677,7 +22686,7 @@
         <v>1.29</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ105">
         <v>1.45</v>
@@ -22805,7 +22814,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22883,7 +22892,7 @@
         <v>2.38</v>
       </c>
       <c r="AP106">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ106">
         <v>2.58</v>
@@ -23011,7 +23020,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23092,7 +23101,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ107">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23298,7 +23307,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
         <v>1.74</v>
@@ -23423,7 +23432,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23835,7 +23844,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23913,10 +23922,10 @@
         <v>1.33</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ111">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
         <v>1.83</v>
@@ -24041,7 +24050,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24247,7 +24256,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24737,7 +24746,7 @@
         <v>1.44</v>
       </c>
       <c r="AP115">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ115">
         <v>1.5</v>
@@ -24943,7 +24952,7 @@
         <v>0.22</v>
       </c>
       <c r="AP116">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ116">
         <v>0.25</v>
@@ -25071,7 +25080,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25277,7 +25286,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25358,7 +25367,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ118">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR118">
         <v>1.62</v>
@@ -25689,7 +25698,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25895,7 +25904,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -26101,7 +26110,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26179,7 +26188,7 @@
         <v>0.9</v>
       </c>
       <c r="AP122">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122">
         <v>0.83</v>
@@ -26307,7 +26316,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26513,7 +26522,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26719,7 +26728,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26800,7 +26809,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ125">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.64</v>
@@ -26925,7 +26934,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27337,7 +27346,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q128">
         <v>3.55</v>
@@ -27415,7 +27424,7 @@
         <v>1.4</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -27543,7 +27552,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q129">
         <v>3.1</v>
@@ -27621,7 +27630,7 @@
         <v>1.9</v>
       </c>
       <c r="AP129">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129">
         <v>1.92</v>
@@ -27749,7 +27758,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q130">
         <v>3.55</v>
@@ -28242,7 +28251,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.82</v>
@@ -28573,7 +28582,7 @@
         <v>171</v>
       </c>
       <c r="P134" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28779,7 +28788,7 @@
         <v>172</v>
       </c>
       <c r="P135" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29191,7 +29200,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29272,7 +29281,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ137">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR137">
         <v>1.52</v>
@@ -29397,7 +29406,7 @@
         <v>139</v>
       </c>
       <c r="P138" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q138">
         <v>2.3</v>
@@ -29809,7 +29818,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q140">
         <v>2.75</v>
@@ -30015,7 +30024,7 @@
         <v>105</v>
       </c>
       <c r="P141" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q141">
         <v>3.4</v>
@@ -30172,6 +30181,624 @@
       </c>
       <c r="BP141">
         <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7806899</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F142">
+        <v>24</v>
+      </c>
+      <c r="G142" t="s">
+        <v>78</v>
+      </c>
+      <c r="H142" t="s">
+        <v>73</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>2</v>
+      </c>
+      <c r="M142">
+        <v>2</v>
+      </c>
+      <c r="N142">
+        <v>4</v>
+      </c>
+      <c r="O142" t="s">
+        <v>177</v>
+      </c>
+      <c r="P142" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q142">
+        <v>3.9</v>
+      </c>
+      <c r="R142">
+        <v>2</v>
+      </c>
+      <c r="S142">
+        <v>2.65</v>
+      </c>
+      <c r="T142">
+        <v>1.43</v>
+      </c>
+      <c r="U142">
+        <v>2.6</v>
+      </c>
+      <c r="V142">
+        <v>3</v>
+      </c>
+      <c r="W142">
+        <v>1.34</v>
+      </c>
+      <c r="X142">
+        <v>8</v>
+      </c>
+      <c r="Y142">
+        <v>1.07</v>
+      </c>
+      <c r="Z142">
+        <v>3.29</v>
+      </c>
+      <c r="AA142">
+        <v>3.15</v>
+      </c>
+      <c r="AB142">
+        <v>2.01</v>
+      </c>
+      <c r="AC142">
+        <v>1.07</v>
+      </c>
+      <c r="AD142">
+        <v>8</v>
+      </c>
+      <c r="AE142">
+        <v>1.38</v>
+      </c>
+      <c r="AF142">
+        <v>3</v>
+      </c>
+      <c r="AG142">
+        <v>1.89</v>
+      </c>
+      <c r="AH142">
+        <v>1.81</v>
+      </c>
+      <c r="AI142">
+        <v>1.85</v>
+      </c>
+      <c r="AJ142">
+        <v>1.83</v>
+      </c>
+      <c r="AK142">
+        <v>1.72</v>
+      </c>
+      <c r="AL142">
+        <v>1.31</v>
+      </c>
+      <c r="AM142">
+        <v>1.29</v>
+      </c>
+      <c r="AN142">
+        <v>1.18</v>
+      </c>
+      <c r="AO142">
+        <v>1.36</v>
+      </c>
+      <c r="AP142">
+        <v>1.17</v>
+      </c>
+      <c r="AQ142">
+        <v>1.33</v>
+      </c>
+      <c r="AR142">
+        <v>1.6</v>
+      </c>
+      <c r="AS142">
+        <v>1.8</v>
+      </c>
+      <c r="AT142">
+        <v>3.4</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>6</v>
+      </c>
+      <c r="AW142">
+        <v>9</v>
+      </c>
+      <c r="AX142">
+        <v>7</v>
+      </c>
+      <c r="AY142">
+        <v>14</v>
+      </c>
+      <c r="AZ142">
+        <v>13</v>
+      </c>
+      <c r="BA142">
+        <v>6</v>
+      </c>
+      <c r="BB142">
+        <v>4</v>
+      </c>
+      <c r="BC142">
+        <v>10</v>
+      </c>
+      <c r="BD142">
+        <v>2.45</v>
+      </c>
+      <c r="BE142">
+        <v>8.5</v>
+      </c>
+      <c r="BF142">
+        <v>1.67</v>
+      </c>
+      <c r="BG142">
+        <v>1.34</v>
+      </c>
+      <c r="BH142">
+        <v>2.87</v>
+      </c>
+      <c r="BI142">
+        <v>1.63</v>
+      </c>
+      <c r="BJ142">
+        <v>2.05</v>
+      </c>
+      <c r="BK142">
+        <v>2.1</v>
+      </c>
+      <c r="BL142">
+        <v>1.61</v>
+      </c>
+      <c r="BM142">
+        <v>2.87</v>
+      </c>
+      <c r="BN142">
+        <v>1.34</v>
+      </c>
+      <c r="BO142">
+        <v>4</v>
+      </c>
+      <c r="BP142">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7806900</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F143">
+        <v>24</v>
+      </c>
+      <c r="G143" t="s">
+        <v>77</v>
+      </c>
+      <c r="H143" t="s">
+        <v>76</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>82</v>
+      </c>
+      <c r="P143" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q143">
+        <v>4</v>
+      </c>
+      <c r="R143">
+        <v>2.05</v>
+      </c>
+      <c r="S143">
+        <v>2.6</v>
+      </c>
+      <c r="T143">
+        <v>1.43</v>
+      </c>
+      <c r="U143">
+        <v>2.6</v>
+      </c>
+      <c r="V143">
+        <v>3</v>
+      </c>
+      <c r="W143">
+        <v>1.34</v>
+      </c>
+      <c r="X143">
+        <v>8</v>
+      </c>
+      <c r="Y143">
+        <v>1.07</v>
+      </c>
+      <c r="Z143">
+        <v>3.64</v>
+      </c>
+      <c r="AA143">
+        <v>3.1</v>
+      </c>
+      <c r="AB143">
+        <v>1.91</v>
+      </c>
+      <c r="AC143">
+        <v>1.07</v>
+      </c>
+      <c r="AD143">
+        <v>8</v>
+      </c>
+      <c r="AE143">
+        <v>1.36</v>
+      </c>
+      <c r="AF143">
+        <v>3.1</v>
+      </c>
+      <c r="AG143">
+        <v>1.9</v>
+      </c>
+      <c r="AH143">
+        <v>1.8</v>
+      </c>
+      <c r="AI143">
+        <v>1.87</v>
+      </c>
+      <c r="AJ143">
+        <v>1.8</v>
+      </c>
+      <c r="AK143">
+        <v>1.75</v>
+      </c>
+      <c r="AL143">
+        <v>1.3</v>
+      </c>
+      <c r="AM143">
+        <v>1.28</v>
+      </c>
+      <c r="AN143">
+        <v>1.45</v>
+      </c>
+      <c r="AO143">
+        <v>1.42</v>
+      </c>
+      <c r="AP143">
+        <v>1.33</v>
+      </c>
+      <c r="AQ143">
+        <v>1.54</v>
+      </c>
+      <c r="AR143">
+        <v>1.42</v>
+      </c>
+      <c r="AS143">
+        <v>1.63</v>
+      </c>
+      <c r="AT143">
+        <v>3.05</v>
+      </c>
+      <c r="AU143">
+        <v>2</v>
+      </c>
+      <c r="AV143">
+        <v>5</v>
+      </c>
+      <c r="AW143">
+        <v>1</v>
+      </c>
+      <c r="AX143">
+        <v>4</v>
+      </c>
+      <c r="AY143">
+        <v>3</v>
+      </c>
+      <c r="AZ143">
+        <v>9</v>
+      </c>
+      <c r="BA143">
+        <v>0</v>
+      </c>
+      <c r="BB143">
+        <v>5</v>
+      </c>
+      <c r="BC143">
+        <v>5</v>
+      </c>
+      <c r="BD143">
+        <v>2.38</v>
+      </c>
+      <c r="BE143">
+        <v>7.5</v>
+      </c>
+      <c r="BF143">
+        <v>1.75</v>
+      </c>
+      <c r="BG143">
+        <v>1.4</v>
+      </c>
+      <c r="BH143">
+        <v>2.6</v>
+      </c>
+      <c r="BI143">
+        <v>1.75</v>
+      </c>
+      <c r="BJ143">
+        <v>1.9</v>
+      </c>
+      <c r="BK143">
+        <v>2.3</v>
+      </c>
+      <c r="BL143">
+        <v>1.5</v>
+      </c>
+      <c r="BM143">
+        <v>3.2</v>
+      </c>
+      <c r="BN143">
+        <v>1.28</v>
+      </c>
+      <c r="BO143">
+        <v>4.25</v>
+      </c>
+      <c r="BP143">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7806901</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F144">
+        <v>24</v>
+      </c>
+      <c r="G144" t="s">
+        <v>75</v>
+      </c>
+      <c r="H144" t="s">
+        <v>70</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
+        <v>82</v>
+      </c>
+      <c r="P144" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q144">
+        <v>3.85</v>
+      </c>
+      <c r="R144">
+        <v>2.05</v>
+      </c>
+      <c r="S144">
+        <v>2.7</v>
+      </c>
+      <c r="T144">
+        <v>1.4</v>
+      </c>
+      <c r="U144">
+        <v>2.75</v>
+      </c>
+      <c r="V144">
+        <v>2.8</v>
+      </c>
+      <c r="W144">
+        <v>1.38</v>
+      </c>
+      <c r="X144">
+        <v>6.45</v>
+      </c>
+      <c r="Y144">
+        <v>1.05</v>
+      </c>
+      <c r="Z144">
+        <v>3.36</v>
+      </c>
+      <c r="AA144">
+        <v>3.27</v>
+      </c>
+      <c r="AB144">
+        <v>1.93</v>
+      </c>
+      <c r="AC144">
+        <v>1.06</v>
+      </c>
+      <c r="AD144">
+        <v>8.5</v>
+      </c>
+      <c r="AE144">
+        <v>1.3</v>
+      </c>
+      <c r="AF144">
+        <v>3.35</v>
+      </c>
+      <c r="AG144">
+        <v>1.88</v>
+      </c>
+      <c r="AH144">
+        <v>1.82</v>
+      </c>
+      <c r="AI144">
+        <v>1.73</v>
+      </c>
+      <c r="AJ144">
+        <v>1.95</v>
+      </c>
+      <c r="AK144">
+        <v>1.77</v>
+      </c>
+      <c r="AL144">
+        <v>1.25</v>
+      </c>
+      <c r="AM144">
+        <v>1.25</v>
+      </c>
+      <c r="AN144">
+        <v>1</v>
+      </c>
+      <c r="AO144">
+        <v>1.18</v>
+      </c>
+      <c r="AP144">
+        <v>0.92</v>
+      </c>
+      <c r="AQ144">
+        <v>1.33</v>
+      </c>
+      <c r="AR144">
+        <v>1.76</v>
+      </c>
+      <c r="AS144">
+        <v>1.42</v>
+      </c>
+      <c r="AT144">
+        <v>3.18</v>
+      </c>
+      <c r="AU144">
+        <v>3</v>
+      </c>
+      <c r="AV144">
+        <v>5</v>
+      </c>
+      <c r="AW144">
+        <v>2</v>
+      </c>
+      <c r="AX144">
+        <v>2</v>
+      </c>
+      <c r="AY144">
+        <v>5</v>
+      </c>
+      <c r="AZ144">
+        <v>7</v>
+      </c>
+      <c r="BA144">
+        <v>3</v>
+      </c>
+      <c r="BB144">
+        <v>3</v>
+      </c>
+      <c r="BC144">
+        <v>6</v>
+      </c>
+      <c r="BD144">
+        <v>2.55</v>
+      </c>
+      <c r="BE144">
+        <v>8.5</v>
+      </c>
+      <c r="BF144">
+        <v>1.75</v>
+      </c>
+      <c r="BG144">
+        <v>1.42</v>
+      </c>
+      <c r="BH144">
+        <v>2.63</v>
+      </c>
+      <c r="BI144">
+        <v>1.71</v>
+      </c>
+      <c r="BJ144">
+        <v>1.98</v>
+      </c>
+      <c r="BK144">
+        <v>2.12</v>
+      </c>
+      <c r="BL144">
+        <v>1.63</v>
+      </c>
+      <c r="BM144">
+        <v>2.7</v>
+      </c>
+      <c r="BN144">
+        <v>1.38</v>
+      </c>
+      <c r="BO144">
+        <v>3.6</v>
+      </c>
+      <c r="BP144">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR9" t="n">
         <v>1.95</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.58</v>
@@ -4184,7 +4184,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR17" t="n">
         <v>1.3</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.83</v>
@@ -8108,7 +8108,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR35" t="n">
         <v>1.17</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.92</v>
@@ -8977,7 +8977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.54</v>
@@ -11811,7 +11811,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.33</v>
@@ -12032,7 +12032,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR53" t="n">
         <v>1.51</v>
@@ -14427,7 +14427,7 @@
         <v>1.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.45</v>
@@ -15520,7 +15520,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR69" t="n">
         <v>1.43</v>
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.33</v>
@@ -17046,7 +17046,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR76" t="n">
         <v>1.63</v>
@@ -20098,7 +20098,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR90" t="n">
         <v>1.6</v>
@@ -20313,7 +20313,7 @@
         <v>1.63</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.5</v>
@@ -22932,7 +22932,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR103" t="n">
         <v>1.74</v>
@@ -25112,7 +25112,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR113" t="n">
         <v>1.6</v>
@@ -27943,7 +27943,7 @@
         <v>0.2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.25</v>
@@ -29690,7 +29690,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR134" t="n">
         <v>1.73</v>
@@ -30559,7 +30559,7 @@
         <v>1.82</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.92</v>
@@ -30792,22 +30792,22 @@
         <v>3.4</v>
       </c>
       <c r="AU139" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW139" t="n">
         <v>9</v>
       </c>
-      <c r="AV139" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW139" t="n">
-        <v>11</v>
-      </c>
       <c r="AX139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY139" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ139" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA139" t="n">
         <v>5</v>
@@ -31010,22 +31010,22 @@
         <v>3.15</v>
       </c>
       <c r="AU140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV140" t="n">
         <v>6</v>
       </c>
       <c r="AW140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ140" t="n">
         <v>12</v>
-      </c>
-      <c r="AY140" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ140" t="n">
-        <v>18</v>
       </c>
       <c r="BA140" t="n">
         <v>6</v>
@@ -31228,22 +31228,22 @@
         <v>2.89</v>
       </c>
       <c r="AU141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV141" t="n">
         <v>4</v>
       </c>
       <c r="AW141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX141" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY141" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ141" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA141" t="n">
         <v>6</v>
@@ -31946,6 +31946,224 @@
       </c>
       <c r="BP144" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>7806876</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45871.29166666666</v>
+      </c>
+      <c r="F145" t="n">
+        <v>20</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>3</v>
+      </c>
+      <c r="N145" t="n">
+        <v>5</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>['50', '63']</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>['59', '67', '70']</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U145" t="n">
+        <v>3</v>
+      </c>
+      <c r="V145" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X145" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>11</v>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
         <v>7</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -1156,10 +1156,10 @@
         <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
         <v>1</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
         <v>8</v>
@@ -1374,10 +1374,10 @@
         <v>2</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
         <v>3</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>12</v>
@@ -1592,10 +1592,10 @@
         <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -2028,10 +2028,10 @@
         <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
         <v>3</v>
@@ -2225,19 +2225,19 @@
         <v>1.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV8" t="n">
         <v>5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -2246,10 +2246,10 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -2443,19 +2443,19 @@
         <v>0.83</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW9" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
         <v>2</v>
       </c>
       <c r="AY9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
         <v>9</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AU10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2682,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
         <v>5</v>
@@ -2900,10 +2900,10 @@
         <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
         <v>5</v>
@@ -3097,19 +3097,19 @@
         <v>1.45</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>6</v>
@@ -3118,10 +3118,10 @@
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
         <v>4</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>11</v>
@@ -3336,10 +3336,10 @@
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -3533,19 +3533,19 @@
         <v>2.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>7</v>
@@ -3554,10 +3554,10 @@
         <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3751,19 +3751,19 @@
         <v>0.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3969,19 +3969,19 @@
         <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3990,10 +3990,10 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>2</v>
@@ -4187,16 +4187,16 @@
         <v>0.83</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -4205,13 +4205,13 @@
         <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
         <v>2</v>
@@ -4405,19 +4405,19 @@
         <v>0.83</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
@@ -4426,10 +4426,10 @@
         <v>5</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA18" t="n">
         <v>6</v>
@@ -4623,13 +4623,13 @@
         <v>1.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
@@ -4638,16 +4638,16 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
         <v>0</v>
@@ -4844,16 +4844,16 @@
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AU20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV20" t="n">
         <v>5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>4</v>
@@ -4862,10 +4862,10 @@
         <v>4</v>
       </c>
       <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>10</v>
       </c>
       <c r="BA20" t="n">
         <v>4</v>
@@ -5059,19 +5059,19 @@
         <v>1.92</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
         <v>11</v>
@@ -5080,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="AY21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
         <v>6</v>
@@ -5280,16 +5280,16 @@
         <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
         <v>3</v>
@@ -5298,10 +5298,10 @@
         <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>5</v>
@@ -5495,19 +5495,19 @@
         <v>0.83</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.87</v>
+        <v>3.61</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW23" t="n">
         <v>11</v>
@@ -5516,10 +5516,10 @@
         <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -5713,19 +5713,19 @@
         <v>1.33</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
@@ -5734,10 +5734,10 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
         <v>5</v>
@@ -5931,19 +5931,19 @@
         <v>1.92</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AU25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -5952,10 +5952,10 @@
         <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>1</v>
@@ -6149,19 +6149,19 @@
         <v>1.54</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AU26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
         <v>4</v>
@@ -6170,10 +6170,10 @@
         <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>1</v>
@@ -6367,19 +6367,19 @@
         <v>1</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="AU27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
         <v>8</v>
@@ -6388,10 +6388,10 @@
         <v>7</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
@@ -6585,19 +6585,19 @@
         <v>1.33</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -6606,10 +6606,10 @@
         <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
         <v>1</v>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
         <v>9</v>
@@ -6824,10 +6824,10 @@
         <v>8</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -7021,19 +7021,19 @@
         <v>1.33</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -7042,10 +7042,10 @@
         <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -7239,19 +7239,19 @@
         <v>1.33</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV31" t="n">
         <v>6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>7</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -7260,10 +7260,10 @@
         <v>5</v>
       </c>
       <c r="AY31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>6</v>
@@ -7457,31 +7457,31 @@
         <v>0.25</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AU32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>3</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4</v>
       </c>
       <c r="BA32" t="n">
         <v>8</v>
@@ -7675,19 +7675,19 @@
         <v>1.33</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="AU33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW33" t="n">
         <v>5</v>
@@ -7696,10 +7696,10 @@
         <v>6</v>
       </c>
       <c r="AY33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA33" t="n">
         <v>5</v>
@@ -7893,19 +7893,19 @@
         <v>1.45</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW34" t="n">
         <v>4</v>
@@ -7914,10 +7914,10 @@
         <v>5</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA34" t="n">
         <v>6</v>
@@ -8111,16 +8111,16 @@
         <v>0.83</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AU35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
         <v>0</v>
@@ -8129,13 +8129,13 @@
         <v>5</v>
       </c>
       <c r="AX35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA35" t="n">
         <v>4</v>
@@ -8329,16 +8329,16 @@
         <v>1.33</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AU36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV36" t="n">
         <v>0</v>
@@ -8347,13 +8347,13 @@
         <v>9</v>
       </c>
       <c r="AX36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA36" t="n">
         <v>4</v>
@@ -8547,19 +8547,19 @@
         <v>2.58</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW37" t="n">
         <v>5</v>
@@ -8568,10 +8568,10 @@
         <v>3</v>
       </c>
       <c r="AY37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA37" t="n">
         <v>7</v>
@@ -8765,19 +8765,19 @@
         <v>1.92</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW38" t="n">
         <v>8</v>
@@ -8786,10 +8786,10 @@
         <v>2</v>
       </c>
       <c r="AY38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA38" t="n">
         <v>5</v>
@@ -8983,19 +8983,19 @@
         <v>1.54</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.76</v>
+        <v>3.49</v>
       </c>
       <c r="AU39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
         <v>8</v>
@@ -9004,10 +9004,10 @@
         <v>10</v>
       </c>
       <c r="AY39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>13</v>
       </c>
       <c r="BA39" t="n">
         <v>2</v>
@@ -9201,19 +9201,19 @@
         <v>0.25</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
         <v>8</v>
@@ -9222,10 +9222,10 @@
         <v>6</v>
       </c>
       <c r="AY40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA40" t="n">
         <v>6</v>
@@ -9419,19 +9419,19 @@
         <v>2.58</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW41" t="n">
         <v>4</v>
@@ -9440,10 +9440,10 @@
         <v>3</v>
       </c>
       <c r="AY41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>7</v>
       </c>
       <c r="BA41" t="n">
         <v>5</v>
@@ -9637,19 +9637,19 @@
         <v>1.33</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW42" t="n">
         <v>7</v>
@@ -9658,10 +9658,10 @@
         <v>11</v>
       </c>
       <c r="AY42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
         <v>1</v>
@@ -9855,19 +9855,19 @@
         <v>1.33</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AU43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW43" t="n">
         <v>8</v>
@@ -9876,10 +9876,10 @@
         <v>7</v>
       </c>
       <c r="AY43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA43" t="n">
         <v>5</v>
@@ -10073,19 +10073,19 @@
         <v>0.83</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AU44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
         <v>3</v>
@@ -10094,10 +10094,10 @@
         <v>3</v>
       </c>
       <c r="AY44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA44" t="n">
         <v>7</v>
@@ -10291,19 +10291,19 @@
         <v>0.25</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW45" t="n">
         <v>1</v>
@@ -10312,10 +10312,10 @@
         <v>8</v>
       </c>
       <c r="AY45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA45" t="n">
         <v>4</v>
@@ -10509,19 +10509,19 @@
         <v>1.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AU46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV46" t="n">
         <v>6</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>7</v>
       </c>
       <c r="AW46" t="n">
         <v>6</v>
@@ -10530,10 +10530,10 @@
         <v>8</v>
       </c>
       <c r="AY46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA46" t="n">
         <v>4</v>
@@ -10727,19 +10727,19 @@
         <v>1.92</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AU47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW47" t="n">
         <v>12</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="AY47" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA47" t="n">
         <v>6</v>
@@ -10945,19 +10945,19 @@
         <v>1</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW48" t="n">
         <v>10</v>
@@ -10966,10 +10966,10 @@
         <v>4</v>
       </c>
       <c r="AY48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA48" t="n">
         <v>1</v>
@@ -11163,19 +11163,19 @@
         <v>1.45</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW49" t="n">
         <v>5</v>
@@ -11184,10 +11184,10 @@
         <v>2</v>
       </c>
       <c r="AY49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA49" t="n">
         <v>5</v>
@@ -11381,19 +11381,19 @@
         <v>0.83</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV50" t="n">
         <v>4</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>5</v>
       </c>
       <c r="AW50" t="n">
         <v>5</v>
@@ -11402,10 +11402,10 @@
         <v>7</v>
       </c>
       <c r="AY50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA50" t="n">
         <v>4</v>
@@ -11599,19 +11599,19 @@
         <v>1.33</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="AU51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV51" t="n">
         <v>3</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>4</v>
       </c>
       <c r="AW51" t="n">
         <v>11</v>
@@ -11620,10 +11620,10 @@
         <v>11</v>
       </c>
       <c r="AY51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>15</v>
       </c>
       <c r="BA51" t="n">
         <v>5</v>
@@ -11817,19 +11817,19 @@
         <v>1.33</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AS52" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="AU52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV52" t="n">
         <v>4</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>5</v>
       </c>
       <c r="AW52" t="n">
         <v>14</v>
@@ -11838,10 +11838,10 @@
         <v>3</v>
       </c>
       <c r="AY52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA52" t="n">
         <v>9</v>
@@ -12035,19 +12035,19 @@
         <v>0.83</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="AU53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV53" t="n">
         <v>7</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>8</v>
       </c>
       <c r="AW53" t="n">
         <v>4</v>
@@ -12056,10 +12056,10 @@
         <v>7</v>
       </c>
       <c r="AY53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA53" t="n">
         <v>3</v>
@@ -12253,19 +12253,19 @@
         <v>1.92</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV54" t="n">
         <v>3</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>4</v>
       </c>
       <c r="AW54" t="n">
         <v>7</v>
@@ -12274,10 +12274,10 @@
         <v>5</v>
       </c>
       <c r="AY54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA54" t="n">
         <v>4</v>
@@ -12471,19 +12471,19 @@
         <v>1.45</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AU55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV55" t="n">
         <v>3</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>4</v>
       </c>
       <c r="AW55" t="n">
         <v>19</v>
@@ -12492,10 +12492,10 @@
         <v>4</v>
       </c>
       <c r="AY55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>1.33</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AU56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV56" t="n">
         <v>4</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>5</v>
       </c>
       <c r="AW56" t="n">
         <v>10</v>
@@ -12710,10 +12710,10 @@
         <v>6</v>
       </c>
       <c r="AY56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA56" t="n">
         <v>8</v>
@@ -12907,19 +12907,19 @@
         <v>0.25</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW57" t="n">
         <v>8</v>
@@ -12928,10 +12928,10 @@
         <v>5</v>
       </c>
       <c r="AY57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA57" t="n">
         <v>5</v>
@@ -13125,19 +13125,19 @@
         <v>1.33</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="AU58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV58" t="n">
         <v>5</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>6</v>
       </c>
       <c r="AW58" t="n">
         <v>11</v>
@@ -13146,10 +13146,10 @@
         <v>10</v>
       </c>
       <c r="AY58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA58" t="n">
         <v>6</v>
@@ -13343,19 +13343,19 @@
         <v>2.58</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="AU59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW59" t="n">
         <v>10</v>
@@ -13364,10 +13364,10 @@
         <v>5</v>
       </c>
       <c r="AY59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA59" t="n">
         <v>2</v>
@@ -13561,19 +13561,19 @@
         <v>0.83</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV60" t="n">
         <v>6</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>7</v>
       </c>
       <c r="AW60" t="n">
         <v>4</v>
@@ -13582,10 +13582,10 @@
         <v>11</v>
       </c>
       <c r="AY60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA60" t="n">
         <v>6</v>
@@ -13779,19 +13779,19 @@
         <v>1.54</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AU61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW61" t="n">
         <v>3</v>
@@ -13800,10 +13800,10 @@
         <v>11</v>
       </c>
       <c r="AY61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ61" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA61" t="n">
         <v>3</v>
@@ -13997,19 +13997,19 @@
         <v>1.33</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.54</v>
+        <v>3.27</v>
       </c>
       <c r="AU62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW62" t="n">
         <v>6</v>
@@ -14018,10 +14018,10 @@
         <v>9</v>
       </c>
       <c r="AY62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA62" t="n">
         <v>7</v>
@@ -14215,16 +14215,16 @@
         <v>1.33</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AU63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV63" t="n">
         <v>0</v>
@@ -14233,13 +14233,13 @@
         <v>5</v>
       </c>
       <c r="AX63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
         <v>4</v>
@@ -14433,19 +14433,19 @@
         <v>1.45</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="AU64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW64" t="n">
         <v>2</v>
@@ -14454,10 +14454,10 @@
         <v>6</v>
       </c>
       <c r="AY64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA64" t="n">
         <v>4</v>
@@ -14651,19 +14651,19 @@
         <v>1.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="AU65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV65" t="n">
         <v>5</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>6</v>
       </c>
       <c r="AW65" t="n">
         <v>4</v>
@@ -14672,10 +14672,10 @@
         <v>5</v>
       </c>
       <c r="AY65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA65" t="n">
         <v>5</v>
@@ -14869,19 +14869,19 @@
         <v>1</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AU66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW66" t="n">
         <v>4</v>
@@ -14890,10 +14890,10 @@
         <v>9</v>
       </c>
       <c r="AY66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA66" t="n">
         <v>4</v>
@@ -15087,19 +15087,19 @@
         <v>0.83</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AU67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW67" t="n">
         <v>8</v>
@@ -15108,10 +15108,10 @@
         <v>9</v>
       </c>
       <c r="AY67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
@@ -15305,19 +15305,19 @@
         <v>2.58</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AU68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW68" t="n">
         <v>11</v>
@@ -15326,10 +15326,10 @@
         <v>1</v>
       </c>
       <c r="AY68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA68" t="n">
         <v>10</v>
@@ -15523,19 +15523,19 @@
         <v>0.83</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AU69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV69" t="n">
         <v>5</v>
-      </c>
-      <c r="AV69" t="n">
-        <v>6</v>
       </c>
       <c r="AW69" t="n">
         <v>11</v>
@@ -15544,10 +15544,10 @@
         <v>7</v>
       </c>
       <c r="AY69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA69" t="n">
         <v>4</v>
@@ -15741,19 +15741,19 @@
         <v>1.33</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="AU70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW70" t="n">
         <v>7</v>
@@ -15762,10 +15762,10 @@
         <v>6</v>
       </c>
       <c r="AY70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA70" t="n">
         <v>6</v>
@@ -15959,19 +15959,19 @@
         <v>1.5</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW71" t="n">
         <v>2</v>
@@ -15980,10 +15980,10 @@
         <v>9</v>
       </c>
       <c r="AY71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ71" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA71" t="n">
         <v>1</v>
@@ -16177,19 +16177,19 @@
         <v>1.92</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="AU72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV72" t="n">
         <v>4</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>5</v>
       </c>
       <c r="AW72" t="n">
         <v>7</v>
@@ -16198,10 +16198,10 @@
         <v>1</v>
       </c>
       <c r="AY72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA72" t="n">
         <v>7</v>
@@ -16395,19 +16395,19 @@
         <v>1.33</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS73" t="n">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AU73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW73" t="n">
         <v>13</v>
@@ -16416,10 +16416,10 @@
         <v>1</v>
       </c>
       <c r="AY73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA73" t="n">
         <v>8</v>
@@ -16613,19 +16613,19 @@
         <v>1.54</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AU74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW74" t="n">
         <v>5</v>
@@ -16634,10 +16634,10 @@
         <v>12</v>
       </c>
       <c r="AY74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ74" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA74" t="n">
         <v>2</v>
@@ -16831,19 +16831,19 @@
         <v>0.25</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AU75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75" t="n">
         <v>7</v>
@@ -16852,10 +16852,10 @@
         <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA75" t="n">
         <v>6</v>
@@ -17049,19 +17049,19 @@
         <v>0.83</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="AU76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW76" t="n">
         <v>10</v>
@@ -17070,10 +17070,10 @@
         <v>7</v>
       </c>
       <c r="AY76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA76" t="n">
         <v>6</v>
@@ -17267,19 +17267,19 @@
         <v>0.25</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW77" t="n">
         <v>10</v>
@@ -17288,10 +17288,10 @@
         <v>5</v>
       </c>
       <c r="AY77" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA77" t="n">
         <v>10</v>
@@ -17485,19 +17485,19 @@
         <v>1.54</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW78" t="n">
         <v>0</v>
@@ -17506,10 +17506,10 @@
         <v>14</v>
       </c>
       <c r="AY78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA78" t="n">
         <v>0</v>
@@ -17703,19 +17703,19 @@
         <v>1.33</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="AU79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW79" t="n">
         <v>10</v>
@@ -17724,10 +17724,10 @@
         <v>4</v>
       </c>
       <c r="AY79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA79" t="n">
         <v>2</v>
@@ -17921,19 +17921,19 @@
         <v>1.5</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="AU80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW80" t="n">
         <v>3</v>
@@ -17942,10 +17942,10 @@
         <v>8</v>
       </c>
       <c r="AY80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA80" t="n">
         <v>2</v>
@@ -18139,19 +18139,19 @@
         <v>2.58</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AU81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW81" t="n">
         <v>9</v>
@@ -18160,10 +18160,10 @@
         <v>2</v>
       </c>
       <c r="AY81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA81" t="n">
         <v>6</v>
@@ -18357,19 +18357,19 @@
         <v>1</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="AU82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW82" t="n">
         <v>6</v>
@@ -18378,10 +18378,10 @@
         <v>7</v>
       </c>
       <c r="AY82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA82" t="n">
         <v>6</v>
@@ -18575,19 +18575,19 @@
         <v>1.33</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT83" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW83" t="n">
         <v>7</v>
@@ -18596,10 +18596,10 @@
         <v>3</v>
       </c>
       <c r="AY83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA83" t="n">
         <v>2</v>
@@ -18793,19 +18793,19 @@
         <v>0.83</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW84" t="n">
         <v>9</v>
@@ -18814,10 +18814,10 @@
         <v>4</v>
       </c>
       <c r="AY84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA84" t="n">
         <v>7</v>
@@ -19011,19 +19011,19 @@
         <v>1.45</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AU85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW85" t="n">
         <v>12</v>
@@ -19032,10 +19032,10 @@
         <v>7</v>
       </c>
       <c r="AY85" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA85" t="n">
         <v>3</v>
@@ -19229,19 +19229,19 @@
         <v>1.54</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="AU86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW86" t="n">
         <v>3</v>
@@ -19250,10 +19250,10 @@
         <v>8</v>
       </c>
       <c r="AY86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA86" t="n">
         <v>7</v>
@@ -19447,19 +19447,19 @@
         <v>1.92</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW87" t="n">
         <v>19</v>
@@ -19468,10 +19468,10 @@
         <v>3</v>
       </c>
       <c r="AY87" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AZ87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA87" t="n">
         <v>8</v>
@@ -19665,19 +19665,19 @@
         <v>2.58</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW88" t="n">
         <v>7</v>
@@ -19686,10 +19686,10 @@
         <v>7</v>
       </c>
       <c r="AY88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ88" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA88" t="n">
         <v>2</v>
@@ -19883,31 +19883,31 @@
         <v>1.33</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU89" t="n">
         <v>0</v>
       </c>
       <c r="AV89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX89" t="n">
         <v>5</v>
       </c>
       <c r="AY89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA89" t="n">
         <v>3</v>
@@ -20101,19 +20101,19 @@
         <v>0.83</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT90" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="AU90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW90" t="n">
         <v>7</v>
@@ -20122,10 +20122,10 @@
         <v>3</v>
       </c>
       <c r="AY90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA90" t="n">
         <v>6</v>
@@ -20319,19 +20319,19 @@
         <v>1.5</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW91" t="n">
         <v>3</v>
@@ -20340,10 +20340,10 @@
         <v>5</v>
       </c>
       <c r="AY91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA91" t="n">
         <v>5</v>
@@ -20537,19 +20537,19 @@
         <v>0.25</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW92" t="n">
         <v>3</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA92" t="n">
         <v>4</v>
@@ -20755,19 +20755,19 @@
         <v>1.33</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS93" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW93" t="n">
         <v>4</v>
@@ -20776,10 +20776,10 @@
         <v>2</v>
       </c>
       <c r="AY93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA93" t="n">
         <v>1</v>
@@ -20973,19 +20973,19 @@
         <v>0.83</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AT94" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="AU94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW94" t="n">
         <v>4</v>
@@ -20994,10 +20994,10 @@
         <v>7</v>
       </c>
       <c r="AY94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA94" t="n">
         <v>4</v>
@@ -21191,19 +21191,19 @@
         <v>1.33</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV95" t="n">
         <v>4</v>
-      </c>
-      <c r="AV95" t="n">
-        <v>5</v>
       </c>
       <c r="AW95" t="n">
         <v>14</v>
@@ -21212,10 +21212,10 @@
         <v>5</v>
       </c>
       <c r="AY95" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA95" t="n">
         <v>1</v>
@@ -21409,19 +21409,19 @@
         <v>2.58</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW96" t="n">
         <v>15</v>
@@ -21430,10 +21430,10 @@
         <v>12</v>
       </c>
       <c r="AY96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ96" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA96" t="n">
         <v>5</v>
@@ -21627,31 +21627,31 @@
         <v>1.54</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV97" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW97" t="n">
         <v>7</v>
       </c>
-      <c r="AW97" t="n">
+      <c r="AX97" t="n">
         <v>3</v>
       </c>
-      <c r="AX97" t="n">
-        <v>1</v>
-      </c>
       <c r="AY97" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA97" t="n">
         <v>5</v>
@@ -21845,31 +21845,31 @@
         <v>1</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="AU98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW98" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY98" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA98" t="n">
         <v>9</v>
@@ -22063,19 +22063,19 @@
         <v>1.33</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AU99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW99" t="n">
         <v>13</v>
@@ -22084,10 +22084,10 @@
         <v>5</v>
       </c>
       <c r="AY99" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA99" t="n">
         <v>7</v>
@@ -22281,31 +22281,31 @@
         <v>1.92</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="AU100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW100" t="n">
         <v>6</v>
       </c>
       <c r="AX100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA100" t="n">
         <v>2</v>
@@ -22499,19 +22499,19 @@
         <v>1.33</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW101" t="n">
         <v>2</v>
@@ -22520,10 +22520,10 @@
         <v>5</v>
       </c>
       <c r="AY101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA101" t="n">
         <v>4</v>
@@ -22717,31 +22717,31 @@
         <v>0.83</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="AU102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW102" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY102" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA102" t="n">
         <v>13</v>
@@ -22935,31 +22935,31 @@
         <v>0.83</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="AU103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW103" t="n">
         <v>5</v>
       </c>
       <c r="AX103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA103" t="n">
         <v>7</v>
@@ -23153,31 +23153,31 @@
         <v>1.33</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS104" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="AU104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY104" t="n">
         <v>6</v>
       </c>
-      <c r="AY104" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA104" t="n">
         <v>4</v>
@@ -23371,31 +23371,31 @@
         <v>1.45</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX105" t="n">
         <v>3</v>
       </c>
-      <c r="AV105" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW105" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>5</v>
-      </c>
       <c r="AY105" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ105" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA105" t="n">
         <v>1</v>
@@ -23589,19 +23589,19 @@
         <v>2.58</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV106" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW106" t="n">
         <v>13</v>
@@ -23610,10 +23610,10 @@
         <v>7</v>
       </c>
       <c r="AY106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ106" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA106" t="n">
         <v>5</v>
@@ -23807,31 +23807,31 @@
         <v>1.54</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX107" t="n">
         <v>5</v>
       </c>
       <c r="AY107" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA107" t="n">
         <v>5</v>
@@ -24025,19 +24025,19 @@
         <v>1.33</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW108" t="n">
         <v>5</v>
@@ -24046,10 +24046,10 @@
         <v>4</v>
       </c>
       <c r="AY108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA108" t="n">
         <v>3</v>
@@ -24243,28 +24243,28 @@
         <v>1</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX109" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ109" t="n">
         <v>13</v>
@@ -24461,31 +24461,31 @@
         <v>0.25</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AU110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY110" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA110" t="n">
         <v>7</v>
@@ -24679,31 +24679,31 @@
         <v>1.33</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AU111" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV111" t="n">
         <v>5</v>
       </c>
-      <c r="AV111" t="n">
-        <v>6</v>
-      </c>
       <c r="AW111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY111" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA111" t="n">
         <v>2</v>
@@ -24897,22 +24897,22 @@
         <v>1.33</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS112" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="AU112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX112" t="n">
         <v>6</v>
@@ -24921,7 +24921,7 @@
         <v>14</v>
       </c>
       <c r="AZ112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA112" t="n">
         <v>5</v>
@@ -25115,19 +25115,19 @@
         <v>0.83</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AU113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW113" t="n">
         <v>5</v>
@@ -25136,10 +25136,10 @@
         <v>5</v>
       </c>
       <c r="AY113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA113" t="n">
         <v>8</v>
@@ -25333,31 +25333,31 @@
         <v>1.45</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="AU114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW114" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ114" t="n">
         <v>7</v>
-      </c>
-      <c r="AX114" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY114" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>10</v>
       </c>
       <c r="BA114" t="n">
         <v>2</v>
@@ -25551,19 +25551,19 @@
         <v>1.5</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
         <v>8</v>
@@ -25572,10 +25572,10 @@
         <v>8</v>
       </c>
       <c r="AY115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA115" t="n">
         <v>7</v>
@@ -25769,31 +25769,31 @@
         <v>0.25</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AU116" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW116" t="n">
         <v>7</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>4</v>
       </c>
       <c r="AX116" t="n">
         <v>4</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA116" t="n">
         <v>7</v>
@@ -25987,31 +25987,31 @@
         <v>0.83</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT117" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AU117" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW117" t="n">
         <v>3</v>
       </c>
       <c r="AX117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY117" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,19 +26205,19 @@
         <v>1.54</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW118" t="n">
         <v>4</v>
@@ -26226,10 +26226,10 @@
         <v>4</v>
       </c>
       <c r="AY118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA118" t="n">
         <v>3</v>
@@ -26423,28 +26423,28 @@
         <v>1</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="AU119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV119" t="n">
         <v>0</v>
       </c>
       <c r="AW119" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX119" t="n">
         <v>8</v>
       </c>
       <c r="AY119" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ119" t="n">
         <v>8</v>
@@ -26641,31 +26641,31 @@
         <v>1.92</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX120" t="n">
         <v>4</v>
       </c>
-      <c r="AV120" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW120" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX120" t="n">
+      <c r="AY120" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ120" t="n">
         <v>9</v>
-      </c>
-      <c r="AY120" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ120" t="n">
-        <v>15</v>
       </c>
       <c r="BA120" t="n">
         <v>4</v>
@@ -26859,31 +26859,31 @@
         <v>2.58</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="AU121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV121" t="n">
         <v>3</v>
       </c>
-      <c r="AV121" t="n">
-        <v>4</v>
-      </c>
       <c r="AW121" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX121" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ121" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA121" t="n">
         <v>7</v>
@@ -27077,31 +27077,31 @@
         <v>0.83</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX122" t="n">
         <v>9</v>
       </c>
       <c r="AY122" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ122" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA122" t="n">
         <v>5</v>
@@ -27295,19 +27295,19 @@
         <v>1.33</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AS123" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="AU123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW123" t="n">
         <v>16</v>
@@ -27316,10 +27316,10 @@
         <v>6</v>
       </c>
       <c r="AY123" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA123" t="n">
         <v>6</v>
@@ -27513,31 +27513,31 @@
         <v>1.45</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="AU124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX124" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY124" t="n">
         <v>8</v>
       </c>
-      <c r="AY124" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ124" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA124" t="n">
         <v>2</v>
@@ -27731,31 +27731,31 @@
         <v>1.33</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AU125" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW125" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY125" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ125" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA125" t="n">
         <v>7</v>
@@ -27949,19 +27949,19 @@
         <v>0.25</v>
       </c>
       <c r="AR126" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="AU126" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW126" t="n">
         <v>17</v>
@@ -27970,10 +27970,10 @@
         <v>4</v>
       </c>
       <c r="AY126" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA126" t="n">
         <v>10</v>
@@ -28167,31 +28167,31 @@
         <v>1.45</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="AU127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW127" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX127" t="n">
         <v>7</v>
       </c>
       <c r="AY127" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA127" t="n">
         <v>2</v>
@@ -28385,31 +28385,31 @@
         <v>1.5</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX128" t="n">
         <v>8</v>
       </c>
       <c r="AY128" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ128" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA128" t="n">
         <v>5</v>
@@ -28603,31 +28603,31 @@
         <v>1.92</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="AU129" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ129" t="n">
         <v>9</v>
-      </c>
-      <c r="AV129" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>10</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
@@ -28821,31 +28821,31 @@
         <v>2.58</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AU130" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV130" t="n">
         <v>8</v>
       </c>
-      <c r="AV130" t="n">
-        <v>9</v>
-      </c>
       <c r="AW130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX130" t="n">
         <v>5</v>
       </c>
       <c r="AY130" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ130" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
@@ -29039,31 +29039,31 @@
         <v>1</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AU131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW131" t="n">
         <v>7</v>
       </c>
-      <c r="AV131" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>5</v>
-      </c>
       <c r="AX131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA131" t="n">
         <v>3</v>
@@ -29257,31 +29257,31 @@
         <v>1.33</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="AU132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW132" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX132" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY132" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ132" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA132" t="n">
         <v>3</v>
@@ -29475,31 +29475,31 @@
         <v>0.25</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AU133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX133" t="n">
         <v>7</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>8</v>
       </c>
       <c r="AY133" t="n">
         <v>15</v>
       </c>
       <c r="AZ133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA133" t="n">
         <v>5</v>
@@ -29693,31 +29693,31 @@
         <v>0.83</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="AU134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY134" t="n">
         <v>8</v>
       </c>
-      <c r="AX134" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ134" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA134" t="n">
         <v>7</v>
@@ -29911,31 +29911,31 @@
         <v>1.5</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY135" t="n">
         <v>4</v>
       </c>
-      <c r="AW135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA135" t="n">
         <v>4</v>
@@ -30129,31 +30129,31 @@
         <v>1.33</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW136" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY136" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA136" t="n">
         <v>7</v>
@@ -30347,31 +30347,31 @@
         <v>1.54</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="AU137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY137" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA137" t="n">
         <v>4</v>
@@ -30565,31 +30565,31 @@
         <v>1.92</v>
       </c>
       <c r="AR138" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AT138" t="n">
-        <v>3.53</v>
+        <v>3.24</v>
       </c>
       <c r="AU138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW138" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX138" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY138" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ138" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA138" t="n">
         <v>7</v>
@@ -30783,22 +30783,22 @@
         <v>0.83</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AU139" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW139" t="n">
         <v>10</v>
-      </c>
-      <c r="AV139" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW139" t="n">
-        <v>9</v>
       </c>
       <c r="AX139" t="n">
         <v>6</v>
@@ -30807,7 +30807,7 @@
         <v>19</v>
       </c>
       <c r="AZ139" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA139" t="n">
         <v>5</v>
@@ -31001,31 +31001,31 @@
         <v>1</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AU140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW140" t="n">
         <v>8</v>
       </c>
       <c r="AX140" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY140" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ140" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA140" t="n">
         <v>6</v>
@@ -31219,31 +31219,31 @@
         <v>2.58</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY141" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA141" t="n">
         <v>6</v>
@@ -31437,31 +31437,31 @@
         <v>1.33</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="AU142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV142" t="n">
         <v>5</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>6</v>
       </c>
       <c r="AW142" t="n">
         <v>9</v>
       </c>
       <c r="AX142" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY142" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ142" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA142" t="n">
         <v>6</v>
@@ -31655,31 +31655,31 @@
         <v>1.54</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY143" t="n">
         <v>5</v>
       </c>
-      <c r="AW143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>3</v>
-      </c>
       <c r="AZ143" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA143" t="n">
         <v>0</v>
@@ -31873,31 +31873,31 @@
         <v>1.33</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="AU144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA144" t="n">
         <v>3</v>
@@ -32091,31 +32091,31 @@
         <v>0.83</v>
       </c>
       <c r="AR145" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT145" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AU145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX145" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY145" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ145" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA145" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP147"/>
+  <dimension ref="A1:BP149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -1786,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
         <v>1.25</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.33</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.58</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR18" t="n">
         <v>2</v>
@@ -4620,7 +4620,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR19" t="n">
         <v>1.33</v>
@@ -5274,7 +5274,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR23" t="n">
         <v>2.06</v>
@@ -6143,7 +6143,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.54</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.92</v>
@@ -8977,7 +8977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.54</v>
@@ -10070,7 +10070,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR44" t="n">
         <v>1.58</v>
@@ -10506,7 +10506,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR46" t="n">
         <v>1.31</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.45</v>
@@ -11378,7 +11378,7 @@
         <v>2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR50" t="n">
         <v>1.55</v>
@@ -11811,7 +11811,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.33</v>
@@ -13558,7 +13558,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR60" t="n">
         <v>1.48</v>
@@ -14427,7 +14427,7 @@
         <v>1.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.45</v>
@@ -14648,7 +14648,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR65" t="n">
         <v>1.52</v>
@@ -15084,7 +15084,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR67" t="n">
         <v>1.87</v>
@@ -15517,7 +15517,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.83</v>
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.33</v>
@@ -15956,7 +15956,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR71" t="n">
         <v>1.52</v>
@@ -17915,10 +17915,10 @@
         <v>1.43</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR80" t="n">
         <v>1.38</v>
@@ -18569,7 +18569,7 @@
         <v>1.86</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.33</v>
@@ -18790,7 +18790,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR84" t="n">
         <v>1.63</v>
@@ -20313,10 +20313,10 @@
         <v>1.63</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR91" t="n">
         <v>1.9</v>
@@ -20970,7 +20970,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR94" t="n">
         <v>1.75</v>
@@ -21839,7 +21839,7 @@
         <v>0.86</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.92</v>
@@ -22714,7 +22714,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -23583,7 +23583,7 @@
         <v>2.38</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ106" t="n">
         <v>2.58</v>
@@ -25548,7 +25548,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
         <v>1.3</v>
@@ -25763,7 +25763,7 @@
         <v>0.22</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.31</v>
@@ -25984,7 +25984,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR117" t="n">
         <v>1.48</v>
@@ -27074,7 +27074,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR122" t="n">
         <v>1.27</v>
@@ -27943,7 +27943,7 @@
         <v>0.2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.31</v>
@@ -28382,7 +28382,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR128" t="n">
         <v>1.67</v>
@@ -28597,7 +28597,7 @@
         <v>1.9</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.92</v>
@@ -29908,7 +29908,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR135" t="n">
         <v>1.37</v>
@@ -30559,7 +30559,7 @@
         <v>1.82</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.92</v>
@@ -30780,7 +30780,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR139" t="n">
         <v>1.65</v>
@@ -31431,7 +31431,7 @@
         <v>1.36</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.33</v>
@@ -32085,7 +32085,7 @@
         <v>0.64</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.83</v>
@@ -32600,6 +32600,442 @@
       </c>
       <c r="BP147" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>7806905</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45878.3125</v>
+      </c>
+      <c r="F148" t="n">
+        <v>25</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V148" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X148" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>7806904</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45878.3125</v>
+      </c>
+      <c r="F149" t="n">
+        <v>25</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S149" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V149" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X149" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP149"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.92</v>
@@ -1350,7 +1350,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR9" t="n">
         <v>1.82</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.33</v>
@@ -3094,7 +3094,7 @@
         <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR12" t="n">
         <v>1.67</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.31</v>
@@ -4181,10 +4181,10 @@
         <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR17" t="n">
         <v>1.17</v>
@@ -6800,7 +6800,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.33</v>
@@ -7887,10 +7887,10 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.45</v>
       </c>
       <c r="AR34" t="n">
         <v>1.45</v>
@@ -8108,7 +8108,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR35" t="n">
         <v>1.04</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.58</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.92</v>
@@ -11160,7 +11160,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR49" t="n">
         <v>1.29</v>
@@ -12032,7 +12032,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR53" t="n">
         <v>1.38</v>
@@ -12468,7 +12468,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR55" t="n">
         <v>1.17</v>
@@ -13773,7 +13773,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.54</v>
@@ -14209,7 +14209,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.33</v>
@@ -14430,7 +14430,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR64" t="n">
         <v>1.93</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.46</v>
@@ -14863,7 +14863,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.92</v>
@@ -15520,7 +15520,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR69" t="n">
         <v>1.3</v>
@@ -17043,10 +17043,10 @@
         <v>0.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR76" t="n">
         <v>1.5</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.54</v>
@@ -19005,10 +19005,10 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR85" t="n">
         <v>1.48</v>
@@ -20098,7 +20098,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR90" t="n">
         <v>1.48</v>
@@ -20531,7 +20531,7 @@
         <v>0.29</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.31</v>
@@ -21185,7 +21185,7 @@
         <v>1.29</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.33</v>
@@ -22932,7 +22932,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR103" t="n">
         <v>1.61</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.33</v>
@@ -23368,7 +23368,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR105" t="n">
         <v>1.7</v>
@@ -25112,7 +25112,7 @@
         <v>2</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR113" t="n">
         <v>1.47</v>
@@ -25330,7 +25330,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR114" t="n">
         <v>1.39</v>
@@ -25545,7 +25545,7 @@
         <v>1.44</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.46</v>
@@ -25981,7 +25981,7 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.77</v>
@@ -27071,7 +27071,7 @@
         <v>0.9</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.77</v>
@@ -27510,7 +27510,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -28164,7 +28164,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR127" t="n">
         <v>1.69</v>
@@ -28815,7 +28815,7 @@
         <v>2.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130" t="n">
         <v>2.58</v>
@@ -29687,10 +29687,10 @@
         <v>0.4</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR134" t="n">
         <v>1.59</v>
@@ -31649,7 +31649,7 @@
         <v>1.42</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.54</v>
@@ -32088,7 +32088,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR145" t="n">
         <v>2</v>
@@ -33036,6 +33036,442 @@
       </c>
       <c r="BP149" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7806907</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F150" t="n">
+        <v>25</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>2</v>
+      </c>
+      <c r="K150" t="n">
+        <v>3</v>
+      </c>
+      <c r="L150" t="n">
+        <v>3</v>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>5</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['1', '76', '83']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>['45+2', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S150" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V150" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X150" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7806906</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F151" t="n">
+        <v>25</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>['45+4']</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>3</v>
+      </c>
+      <c r="R151" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V151" t="n">
+        <v>3</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X151" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -32318,13 +32318,13 @@
         <v>2.74</v>
       </c>
       <c r="AU146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV146" t="n">
         <v>3</v>
       </c>
       <c r="AW146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX146" t="n">
         <v>10</v>
@@ -32536,13 +32536,13 @@
         <v>2.82</v>
       </c>
       <c r="AU147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV147" t="n">
         <v>3</v>
       </c>
       <c r="AW147" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX147" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.54</v>
@@ -2004,7 +2004,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.46</v>
@@ -3312,7 +3312,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.46</v>
@@ -5710,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR24" t="n">
         <v>1.69</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.92</v>
@@ -7018,7 +7018,7 @@
         <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
         <v>1.63</v>
@@ -7236,7 +7236,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR31" t="n">
         <v>1.59</v>
@@ -8105,7 +8105,7 @@
         <v>0.33</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.77</v>
@@ -8326,7 +8326,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR36" t="n">
         <v>1.8</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ37" t="n">
         <v>2.58</v>
@@ -9634,7 +9634,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
         <v>1.07</v>
@@ -9849,10 +9849,10 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR43" t="n">
         <v>1.11</v>
@@ -11814,7 +11814,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR52" t="n">
         <v>1.91</v>
@@ -12029,7 +12029,7 @@
         <v>0.25</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.77</v>
@@ -12683,10 +12683,10 @@
         <v>1.25</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR56" t="n">
         <v>1.11</v>
@@ -13119,7 +13119,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.33</v>
@@ -13555,7 +13555,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.77</v>
@@ -14212,7 +14212,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR63" t="n">
         <v>1.32</v>
@@ -15738,7 +15738,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR70" t="n">
         <v>1.93</v>
@@ -16389,10 +16389,10 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR73" t="n">
         <v>1.2</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.54</v>
@@ -17261,7 +17261,7 @@
         <v>0.17</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.31</v>
@@ -17697,7 +17697,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.33</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.58</v>
@@ -19877,10 +19877,10 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR89" t="n">
         <v>1.44</v>
@@ -20752,7 +20752,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR93" t="n">
         <v>1.44</v>
@@ -21188,7 +21188,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR95" t="n">
         <v>1.24</v>
@@ -22275,7 +22275,7 @@
         <v>2.13</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.92</v>
@@ -23150,7 +23150,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR104" t="n">
         <v>1.48</v>
@@ -24022,7 +24022,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR108" t="n">
         <v>1.61</v>
@@ -24455,7 +24455,7 @@
         <v>0.25</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.31</v>
@@ -24676,7 +24676,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR111" t="n">
         <v>1.7</v>
@@ -24894,7 +24894,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR112" t="n">
         <v>1.54</v>
@@ -25327,7 +25327,7 @@
         <v>1.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.33</v>
@@ -27292,7 +27292,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR123" t="n">
         <v>1.64</v>
@@ -27507,7 +27507,7 @@
         <v>1.44</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.33</v>
@@ -27728,7 +27728,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR125" t="n">
         <v>1.53</v>
@@ -29033,7 +29033,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.92</v>
@@ -29469,7 +29469,7 @@
         <v>0.27</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.31</v>
@@ -30126,7 +30126,7 @@
         <v>2</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR136" t="n">
         <v>1.45</v>
@@ -30341,7 +30341,7 @@
         <v>1.55</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.54</v>
@@ -31870,7 +31870,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR144" t="n">
         <v>1.63</v>
@@ -33472,6 +33472,442 @@
       </c>
       <c r="BP151" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>7806908</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45884.29166666666</v>
+      </c>
+      <c r="F152" t="n">
+        <v>26</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S152" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V152" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X152" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>7806909</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45884.29166666666</v>
+      </c>
+      <c r="F153" t="n">
+        <v>26</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>2</v>
+      </c>
+      <c r="S153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V153" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X153" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -33193,13 +33193,13 @@
         <v>5</v>
       </c>
       <c r="AV150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW150" t="n">
         <v>7</v>
       </c>
       <c r="AX150" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY150" t="n">
         <v>12</v>
@@ -33408,16 +33408,16 @@
         <v>2.71</v>
       </c>
       <c r="AU151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY151" t="n">
         <v>9</v>
@@ -33626,16 +33626,16 @@
         <v>2.32</v>
       </c>
       <c r="AU152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV152" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY152" t="n">
         <v>6</v>
@@ -33844,13 +33844,13 @@
         <v>2.68</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV153" t="n">
         <v>1</v>
       </c>
       <c r="AW153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX153" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.46</v>
@@ -2876,7 +2876,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.33</v>
@@ -3748,7 +3748,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR15" t="n">
         <v>1.73</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.54</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.31</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.46</v>
@@ -7454,7 +7454,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR32" t="n">
         <v>0.77</v>
@@ -7672,7 +7672,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR33" t="n">
         <v>1.75</v>
@@ -9198,7 +9198,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR40" t="n">
         <v>1.81</v>
@@ -9631,7 +9631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.46</v>
@@ -10288,7 +10288,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR45" t="n">
         <v>1.64</v>
@@ -10503,7 +10503,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.46</v>
@@ -11375,7 +11375,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.77</v>
@@ -11596,7 +11596,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR51" t="n">
         <v>1.99</v>
@@ -12901,10 +12901,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR57" t="n">
         <v>1.5</v>
@@ -13122,7 +13122,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR58" t="n">
         <v>1.4</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ59" t="n">
         <v>2.58</v>
@@ -13994,7 +13994,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR62" t="n">
         <v>1.6</v>
@@ -16171,7 +16171,7 @@
         <v>2.67</v>
       </c>
       <c r="AP72" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.92</v>
@@ -16825,10 +16825,10 @@
         <v>0.2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR75" t="n">
         <v>1.41</v>
@@ -17264,7 +17264,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR77" t="n">
         <v>1.38</v>
@@ -17700,7 +17700,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR79" t="n">
         <v>1.36</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.92</v>
@@ -18572,7 +18572,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR83" t="n">
         <v>1.33</v>
@@ -19441,7 +19441,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.92</v>
@@ -20534,7 +20534,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR92" t="n">
         <v>1.21</v>
@@ -20967,7 +20967,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.77</v>
@@ -22060,7 +22060,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22493,10 +22493,10 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR101" t="n">
         <v>1.47</v>
@@ -24237,7 +24237,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.92</v>
@@ -24458,7 +24458,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR110" t="n">
         <v>1.37</v>
@@ -25109,7 +25109,7 @@
         <v>0.44</v>
       </c>
       <c r="AP113" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.77</v>
@@ -25766,7 +25766,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR116" t="n">
         <v>1.43</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.54</v>
@@ -27289,7 +27289,7 @@
         <v>1.3</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.31</v>
@@ -27946,7 +27946,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR126" t="n">
         <v>1.87</v>
@@ -28161,7 +28161,7 @@
         <v>1.6</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.33</v>
@@ -29254,7 +29254,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR132" t="n">
         <v>1.67</v>
@@ -29472,7 +29472,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR133" t="n">
         <v>1.37</v>
@@ -30123,7 +30123,7 @@
         <v>1.45</v>
       </c>
       <c r="AP136" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.31</v>
@@ -30995,7 +30995,7 @@
         <v>1.09</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.92</v>
@@ -31434,7 +31434,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR142" t="n">
         <v>1.48</v>
@@ -32306,7 +32306,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR146" t="n">
         <v>1.6</v>
@@ -32521,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="AP147" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.92</v>
@@ -33629,13 +33629,13 @@
         <v>2</v>
       </c>
       <c r="AV152" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW152" t="n">
         <v>4</v>
       </c>
       <c r="AX152" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY152" t="n">
         <v>6</v>
@@ -33844,16 +33844,16 @@
         <v>2.68</v>
       </c>
       <c r="AU153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY153" t="n">
         <v>8</v>
@@ -33908,6 +33908,442 @@
       </c>
       <c r="BP153" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>7806910</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F154" t="n">
+        <v>26</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>3</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['27', '55', '83']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S154" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U154" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X154" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>7806911</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45885.33333333334</v>
+      </c>
+      <c r="F155" t="n">
+        <v>26</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" t="n">
+        <v>4</v>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
+        <v>6</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['2', '61', '75', '90+2']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['6', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S155" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U155" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X155" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -28633,10 +28633,10 @@
         <v>6</v>
       </c>
       <c r="BB129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC129" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD129" t="n">
         <v>1.7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR26" t="n">
         <v>1.51</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.33</v>
@@ -8323,7 +8323,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.31</v>
@@ -8980,7 +8980,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR39" t="n">
         <v>2</v>
@@ -9195,7 +9195,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.29</v>
@@ -12247,7 +12247,7 @@
         <v>2.6</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.92</v>
@@ -13776,7 +13776,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR61" t="n">
         <v>1.67</v>
@@ -13991,7 +13991,7 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.23</v>
@@ -16610,7 +16610,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR74" t="n">
         <v>1.46</v>
@@ -17482,7 +17482,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR78" t="n">
         <v>1.33</v>
@@ -18787,7 +18787,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.77</v>
@@ -19226,7 +19226,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR86" t="n">
         <v>1.81</v>
@@ -21621,10 +21621,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR97" t="n">
         <v>1.61</v>
@@ -22929,7 +22929,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.77</v>
@@ -23804,7 +23804,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR107" t="n">
         <v>1.4</v>
@@ -24019,7 +24019,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.46</v>
@@ -26202,7 +26202,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR118" t="n">
         <v>1.49</v>
@@ -26417,7 +26417,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.92</v>
@@ -26853,7 +26853,7 @@
         <v>2.44</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ121" t="n">
         <v>2.58</v>
@@ -30344,7 +30344,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR137" t="n">
         <v>1.41</v>
@@ -30777,7 +30777,7 @@
         <v>0.91</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.77</v>
@@ -31652,7 +31652,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -34344,6 +34344,224 @@
       </c>
       <c r="BP155" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>7806912</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45886.29166666666</v>
+      </c>
+      <c r="F156" t="n">
+        <v>26</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="n">
+        <v>5</v>
+      </c>
+      <c r="L156" t="n">
+        <v>6</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>8</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['10', '18', '45+4', '52', '90+1', '90+14']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['27', '40']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U156" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X156" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP156"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.77</v>
@@ -3963,7 +3963,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.92</v>
@@ -5056,7 +5056,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR21" t="n">
         <v>1.81</v>
@@ -5928,7 +5928,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR25" t="n">
         <v>1.07</v>
@@ -7233,7 +7233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.46</v>
@@ -8762,7 +8762,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR38" t="n">
         <v>2.08</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.77</v>
@@ -10285,7 +10285,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.29</v>
@@ -10724,7 +10724,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR47" t="n">
         <v>0.88</v>
@@ -12250,7 +12250,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR54" t="n">
         <v>1.75</v>
@@ -15953,7 +15953,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.46</v>
@@ -16174,7 +16174,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR72" t="n">
         <v>1.53</v>
@@ -18133,7 +18133,7 @@
         <v>2.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81" t="n">
         <v>2.58</v>
@@ -19444,7 +19444,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR87" t="n">
         <v>1.47</v>
@@ -20749,7 +20749,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.31</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.23</v>
@@ -22278,7 +22278,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR100" t="n">
         <v>1.39</v>
@@ -23801,7 +23801,7 @@
         <v>1.44</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.43</v>
@@ -26635,10 +26635,10 @@
         <v>2</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
         <v>1.38</v>
@@ -28600,7 +28600,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR129" t="n">
         <v>1.44</v>
@@ -29905,7 +29905,7 @@
         <v>1.55</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.46</v>
@@ -30562,7 +30562,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR138" t="n">
         <v>2.04</v>
@@ -31213,7 +31213,7 @@
         <v>2.55</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ141" t="n">
         <v>2.58</v>
@@ -34562,6 +34562,224 @@
       </c>
       <c r="BP156" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>7806913</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45886.29166666666</v>
+      </c>
+      <c r="F157" t="n">
+        <v>26</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['27', '65']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S157" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X157" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -34498,16 +34498,16 @@
         <v>3.23</v>
       </c>
       <c r="AU156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX156" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY156" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -19674,22 +19674,22 @@
         <v>2.34</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY88" t="n">
         <v>9</v>
       </c>
       <c r="AZ88" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA88" t="n">
         <v>2</v>
@@ -19895,19 +19895,19 @@
         <v>0</v>
       </c>
       <c r="AV89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW89" t="n">
         <v>4</v>
       </c>
-      <c r="AW89" t="n">
-        <v>6</v>
-      </c>
       <c r="AX89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ89" t="n">
         <v>5</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>9</v>
       </c>
       <c r="BA89" t="n">
         <v>3</v>
@@ -20764,7 +20764,7 @@
         <v>2.26</v>
       </c>
       <c r="AU93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
         <v>1</v>
@@ -20776,7 +20776,7 @@
         <v>2</v>
       </c>
       <c r="AY93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ93" t="n">
         <v>3</v>
@@ -21000,13 +21000,13 @@
         <v>9</v>
       </c>
       <c r="BA94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB94" t="n">
         <v>5</v>
       </c>
       <c r="BC94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD94" t="n">
         <v>1.81</v>
@@ -21194,25 +21194,25 @@
         <v>1.24</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX95" t="n">
         <v>4</v>
       </c>
-      <c r="AW95" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX95" t="n">
-        <v>5</v>
-      </c>
       <c r="AY95" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ95" t="n">
         <v>9</v>
@@ -21412,28 +21412,28 @@
         <v>1.72</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="AU96" t="n">
         <v>1</v>
       </c>
       <c r="AV96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW96" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX96" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AY96" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ96" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA96" t="n">
         <v>5</v>
@@ -21854,13 +21854,13 @@
         <v>2.67</v>
       </c>
       <c r="AU98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV98" t="n">
         <v>3</v>
       </c>
       <c r="AW98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX98" t="n">
         <v>6</v>
@@ -22063,22 +22063,22 @@
         <v>1.23</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AS99" t="n">
         <v>1.69</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AU99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV99" t="n">
         <v>3</v>
       </c>
       <c r="AW99" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX99" t="n">
         <v>5</v>
@@ -22281,13 +22281,13 @@
         <v>1.77</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS100" t="n">
         <v>1.12</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AU100" t="n">
         <v>5</v>
@@ -22311,10 +22311,10 @@
         <v>2</v>
       </c>
       <c r="BB100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD100" t="n">
         <v>1.98</v>
@@ -22502,10 +22502,10 @@
         <v>1.47</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AU101" t="n">
         <v>7</v>
@@ -23371,13 +23371,13 @@
         <v>1.33</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AS105" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AU105" t="n">
         <v>2</v>
@@ -23589,31 +23589,31 @@
         <v>2.58</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AU106" t="n">
         <v>3</v>
       </c>
       <c r="AV106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW106" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AX106" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY106" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AZ106" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA106" t="n">
         <v>5</v>
@@ -23807,25 +23807,25 @@
         <v>1.43</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="AU107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY107" t="n">
         <v>8</v>
@@ -24025,13 +24025,13 @@
         <v>1.46</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AU108" t="n">
         <v>6</v>
@@ -24246,10 +24246,10 @@
         <v>1.64</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
@@ -24461,13 +24461,13 @@
         <v>0.29</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS110" t="n">
         <v>1.2</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU110" t="n">
         <v>4</v>
@@ -24679,25 +24679,25 @@
         <v>1.46</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="AU111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX111" t="n">
         <v>4</v>
-      </c>
-      <c r="AV111" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW111" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX111" t="n">
-        <v>5</v>
       </c>
       <c r="AY111" t="n">
         <v>12</v>
@@ -24897,25 +24897,25 @@
         <v>1.31</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AS112" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY112" t="n">
         <v>14</v>
@@ -25115,22 +25115,22 @@
         <v>0.77</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AU113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX113" t="n">
         <v>5</v>
@@ -25139,7 +25139,7 @@
         <v>10</v>
       </c>
       <c r="AZ113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA113" t="n">
         <v>8</v>
@@ -25333,13 +25333,13 @@
         <v>1.33</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AS114" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AU114" t="n">
         <v>4</v>
@@ -25551,31 +25551,31 @@
         <v>1.46</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS115" t="n">
         <v>1.57</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV115" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX115" t="n">
         <v>5</v>
       </c>
-      <c r="AW115" t="n">
+      <c r="AY115" t="n">
         <v>8</v>
       </c>
-      <c r="AX115" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ115" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA115" t="n">
         <v>7</v>
@@ -25769,13 +25769,13 @@
         <v>0.29</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AS116" t="n">
         <v>1.19</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AU116" t="n">
         <v>6</v>
@@ -25987,13 +25987,13 @@
         <v>0.77</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU117" t="n">
         <v>11</v>
@@ -26205,13 +26205,13 @@
         <v>1.43</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AU118" t="n">
         <v>3</v>
@@ -26423,13 +26423,13 @@
         <v>0.92</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AU119" t="n">
         <v>2</v>
@@ -26641,25 +26641,25 @@
         <v>1.77</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AU120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW120" t="n">
         <v>5</v>
       </c>
-      <c r="AW120" t="n">
-        <v>7</v>
-      </c>
       <c r="AX120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY120" t="n">
         <v>10</v>
@@ -26859,25 +26859,25 @@
         <v>2.58</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX121" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY121" t="n">
         <v>15</v>
@@ -27077,25 +27077,25 @@
         <v>0.77</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV122" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX122" t="n">
         <v>10</v>
-      </c>
-      <c r="AW122" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX122" t="n">
-        <v>9</v>
       </c>
       <c r="AY122" t="n">
         <v>12</v>
@@ -27295,13 +27295,13 @@
         <v>1.31</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AS123" t="n">
         <v>0.85</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AU123" t="n">
         <v>5</v>
@@ -27516,22 +27516,22 @@
         <v>1.39</v>
       </c>
       <c r="AS124" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="AU124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV124" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX124" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY124" t="n">
         <v>8</v>
@@ -27731,25 +27731,25 @@
         <v>1.46</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="AU125" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AV125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX125" t="n">
         <v>3</v>
-      </c>
-      <c r="AW125" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>2</v>
       </c>
       <c r="AY125" t="n">
         <v>19</v>
@@ -27958,19 +27958,19 @@
         <v>3.02</v>
       </c>
       <c r="AU126" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV126" t="n">
         <v>4</v>
       </c>
       <c r="AW126" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AX126" t="n">
         <v>4</v>
       </c>
       <c r="AY126" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AZ126" t="n">
         <v>8</v>
@@ -28170,22 +28170,22 @@
         <v>1.69</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV127" t="n">
         <v>4</v>
       </c>
-      <c r="AV127" t="n">
-        <v>3</v>
-      </c>
       <c r="AW127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY127" t="n">
         <v>11</v>
@@ -28385,22 +28385,22 @@
         <v>1.46</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="AU128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV128" t="n">
         <v>6</v>
       </c>
       <c r="AW128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX128" t="n">
         <v>8</v>
@@ -28603,13 +28603,13 @@
         <v>1.77</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="AU129" t="n">
         <v>8</v>
@@ -28633,10 +28633,10 @@
         <v>6</v>
       </c>
       <c r="BB129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC129" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD129" t="n">
         <v>1.7</v>
@@ -28821,13 +28821,13 @@
         <v>2.58</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AU130" t="n">
         <v>7</v>
@@ -29039,13 +29039,13 @@
         <v>0.92</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="AU131" t="n">
         <v>6</v>
@@ -29257,25 +29257,25 @@
         <v>1.23</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="AU132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY132" t="n">
         <v>6</v>
@@ -29475,25 +29475,25 @@
         <v>0.29</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AS133" t="n">
         <v>1.15</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AU133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW133" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX133" t="n">
         <v>9</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>7</v>
       </c>
       <c r="AY133" t="n">
         <v>15</v>
@@ -29693,25 +29693,25 @@
         <v>0.77</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AU134" t="n">
         <v>6</v>
       </c>
       <c r="AV134" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW134" t="n">
         <v>2</v>
       </c>
       <c r="AX134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY134" t="n">
         <v>8</v>
@@ -29911,25 +29911,25 @@
         <v>1.46</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AS135" t="n">
         <v>1.62</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AU135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX135" t="n">
         <v>4</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>6</v>
       </c>
       <c r="AY135" t="n">
         <v>4</v>
@@ -30129,22 +30129,22 @@
         <v>1.31</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AS136" t="n">
         <v>0.89</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AU136" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV136" t="n">
         <v>1</v>
       </c>
       <c r="AW136" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX136" t="n">
         <v>4</v>
@@ -30347,25 +30347,25 @@
         <v>1.43</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AS137" t="n">
         <v>1.55</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY137" t="n">
         <v>16</v>
@@ -30565,25 +30565,25 @@
         <v>1.77</v>
       </c>
       <c r="AR138" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT138" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AU138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX138" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY138" t="n">
         <v>14</v>
@@ -30783,13 +30783,13 @@
         <v>0.77</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="AU139" t="n">
         <v>9</v>
@@ -30819,43 +30819,43 @@
         <v>8</v>
       </c>
       <c r="BD139" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BE139" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF139" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BG139" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BH139" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BI139" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BJ139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BK139" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BL139" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BM139" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BN139" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BO139" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="BP139" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="140">
@@ -31001,13 +31001,13 @@
         <v>0.92</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU140" t="n">
         <v>9</v>
@@ -31219,13 +31219,13 @@
         <v>2.58</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AU141" t="n">
         <v>3</v>
@@ -31255,43 +31255,43 @@
         <v>7</v>
       </c>
       <c r="BD141" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BE141" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="BF141" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BG141" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BH141" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BI141" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BJ141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK141" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BL141" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BM141" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BN141" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BO141" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP141" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="142">
@@ -31437,13 +31437,13 @@
         <v>1.23</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="AU142" t="n">
         <v>4</v>
@@ -31655,25 +31655,25 @@
         <v>1.43</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AS143" t="n">
         <v>1.51</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY143" t="n">
         <v>5</v>
@@ -31873,22 +31873,22 @@
         <v>1.46</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="AU144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV144" t="n">
         <v>4</v>
       </c>
       <c r="AW144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX144" t="n">
         <v>4</v>
@@ -32091,13 +32091,13 @@
         <v>0.77</v>
       </c>
       <c r="AR145" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AT145" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="AU145" t="n">
         <v>3</v>
@@ -32309,13 +32309,13 @@
         <v>0.29</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AU146" t="n">
         <v>5</v>
@@ -32527,10 +32527,10 @@
         <v>0.92</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AT147" t="n">
         <v>2.82</v>
@@ -32745,25 +32745,25 @@
         <v>1.46</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AS148" t="n">
         <v>1.6</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AU148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW148" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY148" t="n">
         <v>9</v>
@@ -32963,25 +32963,25 @@
         <v>0.77</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AT149" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="AU149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW149" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY149" t="n">
         <v>20</v>
@@ -33181,13 +33181,13 @@
         <v>0.77</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AU150" t="n">
         <v>5</v>
@@ -33399,13 +33399,13 @@
         <v>1.33</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU151" t="n">
         <v>5</v>
@@ -33835,22 +33835,22 @@
         <v>1.46</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
         <v>2</v>
       </c>
       <c r="AW153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX153" t="n">
         <v>2</v>
@@ -34053,25 +34053,25 @@
         <v>0.29</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AU154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW154" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX154" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY154" t="n">
         <v>11</v>
@@ -34271,25 +34271,25 @@
         <v>1.23</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="AU155" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AV155" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW155" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX155" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY155" t="n">
         <v>18</v>
@@ -34489,13 +34489,13 @@
         <v>1.43</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AS156" t="n">
         <v>1.53</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="AU156" t="n">
         <v>8</v>
@@ -34707,13 +34707,13 @@
         <v>1.77</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="AU157" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR9" t="n">
         <v>1.82</v>
@@ -3963,7 +3963,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.92</v>
@@ -4184,7 +4184,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR17" t="n">
         <v>1.17</v>
@@ -4402,7 +4402,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR18" t="n">
         <v>2</v>
@@ -5492,7 +5492,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR23" t="n">
         <v>2.06</v>
@@ -5710,7 +5710,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR24" t="n">
         <v>1.69</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.33</v>
@@ -7233,7 +7233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.46</v>
@@ -8108,7 +8108,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR35" t="n">
         <v>1.04</v>
@@ -8323,10 +8323,10 @@
         <v>1.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
         <v>1.8</v>
@@ -9195,7 +9195,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.29</v>
@@ -9852,7 +9852,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR43" t="n">
         <v>1.11</v>
@@ -10067,10 +10067,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR44" t="n">
         <v>1.58</v>
@@ -10285,7 +10285,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.29</v>
@@ -11378,7 +11378,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR50" t="n">
         <v>1.55</v>
@@ -11814,7 +11814,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR52" t="n">
         <v>1.91</v>
@@ -12032,7 +12032,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR53" t="n">
         <v>1.38</v>
@@ -12247,7 +12247,7 @@
         <v>2.6</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.77</v>
@@ -13558,7 +13558,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR60" t="n">
         <v>1.48</v>
@@ -13991,7 +13991,7 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.23</v>
@@ -14212,7 +14212,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR63" t="n">
         <v>1.32</v>
@@ -15084,7 +15084,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR67" t="n">
         <v>1.87</v>
@@ -15520,7 +15520,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR69" t="n">
         <v>1.3</v>
@@ -15953,7 +15953,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.46</v>
@@ -16392,7 +16392,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR73" t="n">
         <v>1.2</v>
@@ -17046,7 +17046,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR76" t="n">
         <v>1.5</v>
@@ -18133,7 +18133,7 @@
         <v>2.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
         <v>2.58</v>
@@ -18787,10 +18787,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR84" t="n">
         <v>1.63</v>
@@ -20098,7 +20098,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR90" t="n">
         <v>1.48</v>
@@ -20749,10 +20749,10 @@
         <v>1.29</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR93" t="n">
         <v>1.44</v>
@@ -20970,7 +20970,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR94" t="n">
         <v>1.75</v>
@@ -21621,7 +21621,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.43</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.23</v>
@@ -22714,7 +22714,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -22929,10 +22929,10 @@
         <v>0.38</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR103" t="n">
         <v>1.61</v>
@@ -23150,7 +23150,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR104" t="n">
         <v>1.48</v>
@@ -23801,7 +23801,7 @@
         <v>1.44</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.43</v>
@@ -24019,7 +24019,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.46</v>
@@ -24894,7 +24894,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR112" t="n">
         <v>1.72</v>
@@ -25112,7 +25112,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR113" t="n">
         <v>1.49</v>
@@ -25984,7 +25984,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR117" t="n">
         <v>1.44</v>
@@ -26417,7 +26417,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.92</v>
@@ -26635,7 +26635,7 @@
         <v>2</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.77</v>
@@ -26853,7 +26853,7 @@
         <v>2.44</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ121" t="n">
         <v>2.58</v>
@@ -27074,7 +27074,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27292,7 +27292,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR123" t="n">
         <v>1.63</v>
@@ -29690,7 +29690,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR134" t="n">
         <v>1.55</v>
@@ -29905,7 +29905,7 @@
         <v>1.55</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.46</v>
@@ -30126,7 +30126,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR136" t="n">
         <v>1.47</v>
@@ -30777,10 +30777,10 @@
         <v>0.91</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR139" t="n">
         <v>1.61</v>
@@ -31213,7 +31213,7 @@
         <v>2.55</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ141" t="n">
         <v>2.58</v>
@@ -32088,7 +32088,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR145" t="n">
         <v>1.92</v>
@@ -32960,7 +32960,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR149" t="n">
         <v>1.9</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR150" t="n">
         <v>1.24</v>
@@ -33614,7 +33614,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR152" t="n">
         <v>1.44</v>
@@ -34483,7 +34483,7 @@
         <v>1.54</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.43</v>
@@ -34701,7 +34701,7 @@
         <v>1.92</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.77</v>
@@ -34780,6 +34780,660 @@
       </c>
       <c r="BP157" t="n">
         <v>1.09</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>7806914</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F158" t="n">
+        <v>27</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>2</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
+        <v>3</v>
+      </c>
+      <c r="L158" t="n">
+        <v>3</v>
+      </c>
+      <c r="M158" t="n">
+        <v>2</v>
+      </c>
+      <c r="N158" t="n">
+        <v>5</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['26', '45+2', '90+2']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>['9', '64']</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>4</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U158" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X158" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7806916</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F159" t="n">
+        <v>27</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>2</v>
+      </c>
+      <c r="N159" t="n">
+        <v>4</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['51', '56']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['48', '54']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S159" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U159" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X159" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7806915</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45892.3125</v>
+      </c>
+      <c r="F160" t="n">
+        <v>27</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X160" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.92</v>
@@ -2876,7 +2876,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR14" t="n">
         <v>2.38</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.29</v>
@@ -4617,7 +4617,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.46</v>
@@ -5056,7 +5056,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
         <v>1.81</v>
@@ -5271,7 +5271,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.46</v>
@@ -5928,7 +5928,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR25" t="n">
         <v>1.07</v>
@@ -6582,7 +6582,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.29</v>
@@ -7669,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR33" t="n">
         <v>1.75</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR37" t="n">
         <v>1.13</v>
@@ -8762,7 +8762,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR38" t="n">
         <v>2.08</v>
@@ -9416,7 +9416,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR41" t="n">
         <v>1.41</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.43</v>
@@ -10721,10 +10721,10 @@
         <v>3</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR47" t="n">
         <v>0.88</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.92</v>
@@ -11596,7 +11596,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR51" t="n">
         <v>1.99</v>
@@ -12029,7 +12029,7 @@
         <v>0.25</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.71</v>
@@ -12250,7 +12250,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR54" t="n">
         <v>1.75</v>
@@ -12465,7 +12465,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.33</v>
@@ -13119,10 +13119,10 @@
         <v>1.75</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR58" t="n">
         <v>1.4</v>
@@ -13340,7 +13340,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR59" t="n">
         <v>1.35</v>
@@ -13555,7 +13555,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.79</v>
@@ -13773,7 +13773,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.43</v>
@@ -13994,7 +13994,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR62" t="n">
         <v>1.6</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.46</v>
@@ -15299,10 +15299,10 @@
         <v>2.25</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR68" t="n">
         <v>1.36</v>
@@ -16174,7 +16174,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR72" t="n">
         <v>1.53</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.43</v>
@@ -17043,7 +17043,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.71</v>
@@ -17261,7 +17261,7 @@
         <v>0.17</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.29</v>
@@ -17700,7 +17700,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR79" t="n">
         <v>1.36</v>
@@ -18136,7 +18136,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR81" t="n">
         <v>1.36</v>
@@ -18572,7 +18572,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR83" t="n">
         <v>1.33</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.33</v>
@@ -19444,7 +19444,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR87" t="n">
         <v>1.47</v>
@@ -19662,7 +19662,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR88" t="n">
         <v>1.39</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.46</v>
@@ -20095,7 +20095,7 @@
         <v>0.29</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.71</v>
@@ -21406,7 +21406,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ96" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR96" t="n">
         <v>1.72</v>
@@ -22060,7 +22060,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR99" t="n">
         <v>1.42</v>
@@ -22275,10 +22275,10 @@
         <v>2.13</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR100" t="n">
         <v>1.37</v>
@@ -22496,7 +22496,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR101" t="n">
         <v>1.47</v>
@@ -22711,7 +22711,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.79</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.43</v>
@@ -23586,7 +23586,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR106" t="n">
         <v>1.39</v>
@@ -24891,7 +24891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.43</v>
@@ -25981,7 +25981,7 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.79</v>
@@ -26638,7 +26638,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR120" t="n">
         <v>1.51</v>
@@ -26856,7 +26856,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ121" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR121" t="n">
         <v>1.59</v>
@@ -27507,7 +27507,7 @@
         <v>1.44</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.33</v>
@@ -27725,7 +27725,7 @@
         <v>1.3</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.46</v>
@@ -28600,7 +28600,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -28815,10 +28815,10 @@
         <v>2.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR130" t="n">
         <v>1.52</v>
@@ -29251,10 +29251,10 @@
         <v>1.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR132" t="n">
         <v>1.79</v>
@@ -29469,7 +29469,7 @@
         <v>0.27</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.29</v>
@@ -29687,7 +29687,7 @@
         <v>0.4</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.71</v>
@@ -30562,7 +30562,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR138" t="n">
         <v>1.96</v>
@@ -31216,7 +31216,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AR141" t="n">
         <v>1.46</v>
@@ -31434,7 +31434,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR142" t="n">
         <v>1.43</v>
@@ -32303,7 +32303,7 @@
         <v>0.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.29</v>
@@ -33393,7 +33393,7 @@
         <v>1.45</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.33</v>
@@ -33829,7 +33829,7 @@
         <v>1.33</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.46</v>
@@ -34268,7 +34268,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR155" t="n">
         <v>1.67</v>
@@ -34704,7 +34704,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR157" t="n">
         <v>1.46</v>
@@ -35370,22 +35370,22 @@
         <v>2.38</v>
       </c>
       <c r="AU160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV160" t="n">
         <v>3</v>
       </c>
       <c r="AW160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX160" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY160" t="n">
         <v>5</v>
       </c>
       <c r="AZ160" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA160" t="n">
         <v>2</v>
@@ -35434,6 +35434,660 @@
       </c>
       <c r="BP160" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7806919</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F161" t="n">
+        <v>27</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>2</v>
+      </c>
+      <c r="L161" t="n">
+        <v>3</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['45+3', '75', '90+2']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['1', '59']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7806918</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F162" t="n">
+        <v>27</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>3</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>4</v>
+      </c>
+      <c r="L162" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>4</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['1', '24', '45']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V162" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X162" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7806917</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F163" t="n">
+        <v>27</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="n">
+        <v>4</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>5</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>['7', '31', '39']</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['23', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S163" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V163" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X163" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -35594,16 +35594,16 @@
         <v>4</v>
       </c>
       <c r="AW161" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX161" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY161" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ161" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA161" t="n">
         <v>6</v>
@@ -35812,13 +35812,13 @@
         <v>5</v>
       </c>
       <c r="AW162" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX162" t="n">
         <v>0</v>
       </c>
       <c r="AY162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ162" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -35594,16 +35594,16 @@
         <v>4</v>
       </c>
       <c r="AW161" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY161" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ161" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA161" t="n">
         <v>6</v>
@@ -35812,13 +35812,13 @@
         <v>5</v>
       </c>
       <c r="AW162" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX162" t="n">
         <v>0</v>
       </c>
       <c r="AY162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ162" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -35588,22 +35588,22 @@
         <v>2.65</v>
       </c>
       <c r="AU161" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV161" t="n">
         <v>5</v>
       </c>
-      <c r="AV161" t="n">
-        <v>4</v>
-      </c>
       <c r="AW161" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AX161" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY161" t="n">
         <v>21</v>
       </c>
       <c r="AZ161" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA161" t="n">
         <v>6</v>
@@ -35806,22 +35806,22 @@
         <v>2.71</v>
       </c>
       <c r="AU162" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX162" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ162" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA162" t="n">
         <v>2</v>
@@ -36024,19 +36024,19 @@
         <v>3.33</v>
       </c>
       <c r="AU163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW163" t="n">
         <v>4</v>
       </c>
       <c r="AX163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ163" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.43</v>
@@ -1350,7 +1350,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.43</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.46</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR9" t="n">
         <v>1.82</v>
@@ -3094,7 +3094,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR12" t="n">
         <v>1.67</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR14" t="n">
         <v>2.38</v>
@@ -4184,7 +4184,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR17" t="n">
         <v>1.17</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.64</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.79</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.64</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.92</v>
@@ -6800,7 +6800,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7890,7 +7890,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR34" t="n">
         <v>1.45</v>
@@ -8105,10 +8105,10 @@
         <v>0.33</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR35" t="n">
         <v>1.04</v>
@@ -8544,7 +8544,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR37" t="n">
         <v>1.13</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.64</v>
@@ -8977,7 +8977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.43</v>
@@ -9416,7 +9416,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR41" t="n">
         <v>1.41</v>
@@ -11160,7 +11160,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR49" t="n">
         <v>1.29</v>
@@ -11593,7 +11593,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.14</v>
@@ -11811,7 +11811,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.43</v>
@@ -12032,7 +12032,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR53" t="n">
         <v>1.38</v>
@@ -12468,7 +12468,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR55" t="n">
         <v>1.17</v>
@@ -12683,7 +12683,7 @@
         <v>1.25</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.46</v>
@@ -13340,7 +13340,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR59" t="n">
         <v>1.35</v>
@@ -14427,10 +14427,10 @@
         <v>1.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR64" t="n">
         <v>1.93</v>
@@ -15081,7 +15081,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.79</v>
@@ -15302,7 +15302,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR68" t="n">
         <v>1.36</v>
@@ -15520,7 +15520,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR69" t="n">
         <v>1.3</v>
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.46</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.43</v>
@@ -17046,7 +17046,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR76" t="n">
         <v>1.5</v>
@@ -17697,7 +17697,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.14</v>
@@ -18136,7 +18136,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR81" t="n">
         <v>1.36</v>
@@ -19008,7 +19008,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR85" t="n">
         <v>1.48</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.43</v>
@@ -19659,10 +19659,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR88" t="n">
         <v>1.39</v>
@@ -20098,7 +20098,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR90" t="n">
         <v>1.48</v>
@@ -20313,7 +20313,7 @@
         <v>1.63</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.46</v>
@@ -21403,10 +21403,10 @@
         <v>2.29</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ96" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR96" t="n">
         <v>1.72</v>
@@ -22932,7 +22932,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR103" t="n">
         <v>1.61</v>
@@ -23365,10 +23365,10 @@
         <v>1.29</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR105" t="n">
         <v>1.64</v>
@@ -23586,7 +23586,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR106" t="n">
         <v>1.39</v>
@@ -24455,7 +24455,7 @@
         <v>0.25</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.29</v>
@@ -24673,7 +24673,7 @@
         <v>1.33</v>
       </c>
       <c r="AP111" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.46</v>
@@ -25112,7 +25112,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR113" t="n">
         <v>1.49</v>
@@ -25327,10 +25327,10 @@
         <v>1.25</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR114" t="n">
         <v>1.38</v>
@@ -26856,7 +26856,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ121" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR121" t="n">
         <v>1.59</v>
@@ -27510,7 +27510,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -27943,7 +27943,7 @@
         <v>0.2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.29</v>
@@ -28164,7 +28164,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR127" t="n">
         <v>1.69</v>
@@ -28379,7 +28379,7 @@
         <v>1.4</v>
       </c>
       <c r="AP128" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.46</v>
@@ -28818,7 +28818,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ130" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR130" t="n">
         <v>1.52</v>
@@ -29033,7 +29033,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.92</v>
@@ -29690,7 +29690,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR134" t="n">
         <v>1.55</v>
@@ -30341,7 +30341,7 @@
         <v>1.55</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.43</v>
@@ -30559,7 +30559,7 @@
         <v>1.82</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.64</v>
@@ -31216,7 +31216,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR141" t="n">
         <v>1.46</v>
@@ -31867,7 +31867,7 @@
         <v>1.18</v>
       </c>
       <c r="AP144" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.46</v>
@@ -32085,10 +32085,10 @@
         <v>0.64</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR145" t="n">
         <v>1.92</v>
@@ -32957,7 +32957,7 @@
         <v>0.83</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.79</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR150" t="n">
         <v>1.24</v>
@@ -33396,7 +33396,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR151" t="n">
         <v>1.56</v>
@@ -33611,7 +33611,7 @@
         <v>1.33</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.43</v>
@@ -34922,7 +34922,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR158" t="n">
         <v>1.67</v>
@@ -35137,7 +35137,7 @@
         <v>0.77</v>
       </c>
       <c r="AP159" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.79</v>
@@ -35794,7 +35794,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ162" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AR162" t="n">
         <v>1.53</v>
@@ -36088,6 +36088,660 @@
       </c>
       <c r="BP163" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7806920</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F164" t="n">
+        <v>28</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['54', '59']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S164" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U164" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X164" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7806921</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F165" t="n">
+        <v>28</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>3</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['80', '90+4', '90+8']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X165" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7806922</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F166" t="n">
+        <v>28</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X166" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36242,16 +36242,16 @@
         <v>3.12</v>
       </c>
       <c r="AU164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW164" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY164" t="n">
         <v>12</v>
@@ -36460,16 +36460,16 @@
         <v>2.88</v>
       </c>
       <c r="AU165" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW165" t="n">
         <v>3</v>
       </c>
-      <c r="AW165" t="n">
-        <v>7</v>
-      </c>
       <c r="AX165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY165" t="n">
         <v>11</v>
@@ -36678,16 +36678,16 @@
         <v>2.51</v>
       </c>
       <c r="AU166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW166" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY166" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR8" t="n">
         <v>1.25</v>
@@ -2655,10 +2655,10 @@
         <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.14</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR16" t="n">
         <v>1.67</v>
@@ -4181,7 +4181,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.67</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.79</v>
@@ -4617,10 +4617,10 @@
         <v>1.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR19" t="n">
         <v>1.33</v>
@@ -5274,7 +5274,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.43</v>
@@ -6364,7 +6364,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR27" t="n">
         <v>1.88</v>
@@ -7018,7 +7018,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR30" t="n">
         <v>1.63</v>
@@ -7236,7 +7236,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR31" t="n">
         <v>1.59</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.29</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.46</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.43</v>
@@ -9634,7 +9634,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR42" t="n">
         <v>1.07</v>
@@ -10506,7 +10506,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR46" t="n">
         <v>1.31</v>
@@ -10721,7 +10721,7 @@
         <v>3</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.64</v>
@@ -10942,7 +10942,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR48" t="n">
         <v>1.55</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.46</v>
@@ -12465,7 +12465,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.46</v>
@@ -12686,7 +12686,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR56" t="n">
         <v>1.11</v>
@@ -14209,7 +14209,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.43</v>
@@ -14648,7 +14648,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR65" t="n">
         <v>1.52</v>
@@ -14863,10 +14863,10 @@
         <v>1.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR66" t="n">
         <v>1.33</v>
@@ -15299,7 +15299,7 @@
         <v>2.25</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.43</v>
@@ -15517,7 +15517,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.67</v>
@@ -15738,7 +15738,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR70" t="n">
         <v>1.93</v>
@@ -15956,7 +15956,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR71" t="n">
         <v>1.52</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.43</v>
@@ -17915,10 +17915,10 @@
         <v>1.43</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR80" t="n">
         <v>1.38</v>
@@ -18354,7 +18354,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR82" t="n">
         <v>1.52</v>
@@ -18569,7 +18569,7 @@
         <v>1.86</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.14</v>
@@ -19880,7 +19880,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR89" t="n">
         <v>1.44</v>
@@ -20095,7 +20095,7 @@
         <v>0.29</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.67</v>
@@ -20316,7 +20316,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
         <v>1.9</v>
@@ -20531,7 +20531,7 @@
         <v>0.29</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.29</v>
@@ -21185,10 +21185,10 @@
         <v>1.29</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR95" t="n">
         <v>1.24</v>
@@ -21839,10 +21839,10 @@
         <v>0.86</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR98" t="n">
         <v>1.36</v>
@@ -22711,7 +22711,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.79</v>
@@ -23583,7 +23583,7 @@
         <v>2.38</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ106" t="n">
         <v>2.43</v>
@@ -24022,7 +24022,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR108" t="n">
         <v>1.56</v>
@@ -24240,7 +24240,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR109" t="n">
         <v>1.64</v>
@@ -24676,7 +24676,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR111" t="n">
         <v>1.58</v>
@@ -24891,7 +24891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.43</v>
@@ -25545,10 +25545,10 @@
         <v>1.44</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR115" t="n">
         <v>1.27</v>
@@ -25763,7 +25763,7 @@
         <v>0.22</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.29</v>
@@ -26420,7 +26420,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR119" t="n">
         <v>1.57</v>
@@ -27071,7 +27071,7 @@
         <v>0.9</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.79</v>
@@ -27725,10 +27725,10 @@
         <v>1.3</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR125" t="n">
         <v>1.7</v>
@@ -28382,7 +28382,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR128" t="n">
         <v>1.57</v>
@@ -28597,7 +28597,7 @@
         <v>1.9</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.64</v>
@@ -29036,7 +29036,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR131" t="n">
         <v>1.38</v>
@@ -29251,7 +29251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.14</v>
@@ -29908,7 +29908,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR135" t="n">
         <v>1.5</v>
@@ -30998,7 +30998,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR140" t="n">
         <v>1.64</v>
@@ -31431,7 +31431,7 @@
         <v>1.36</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.14</v>
@@ -31649,7 +31649,7 @@
         <v>1.42</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.43</v>
@@ -31870,7 +31870,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR144" t="n">
         <v>1.55</v>
@@ -32303,7 +32303,7 @@
         <v>0.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.29</v>
@@ -32524,7 +32524,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR147" t="n">
         <v>1.56</v>
@@ -32739,10 +32739,10 @@
         <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR148" t="n">
         <v>1.44</v>
@@ -33175,7 +33175,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.67</v>
@@ -33832,7 +33832,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR153" t="n">
         <v>1.4</v>
@@ -36009,7 +36009,7 @@
         <v>1.23</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.14</v>
@@ -36742,6 +36742,660 @@
       </c>
       <c r="BP166" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7806923</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F167" t="n">
+        <v>28</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['4', '79']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S167" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X167" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7806924</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F168" t="n">
+        <v>28</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S168" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V168" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X168" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7806925</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F169" t="n">
+        <v>28</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>2</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>3</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>['63', '90+8']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S169" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X169" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36869,7 +36869,7 @@
         <v>1.29</v>
       </c>
       <c r="AL167" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM167" t="n">
         <v>2.1</v>
@@ -37087,7 +37087,7 @@
         <v>1.33</v>
       </c>
       <c r="AL168" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM168" t="n">
         <v>1.44</v>
@@ -37305,7 +37305,7 @@
         <v>1.3</v>
       </c>
       <c r="AL169" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM169" t="n">
         <v>1.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36242,16 +36242,16 @@
         <v>3.12</v>
       </c>
       <c r="AU164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV164" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW164" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX164" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY164" t="n">
         <v>12</v>
@@ -36460,16 +36460,16 @@
         <v>2.88</v>
       </c>
       <c r="AU165" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW165" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY165" t="n">
         <v>11</v>
@@ -36678,16 +36678,16 @@
         <v>2.51</v>
       </c>
       <c r="AU166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW166" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY166" t="n">
         <v>12</v>
@@ -36896,16 +36896,16 @@
         <v>2.96</v>
       </c>
       <c r="AU167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV167" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW167" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY167" t="n">
         <v>18</v>
@@ -37114,16 +37114,16 @@
         <v>2.64</v>
       </c>
       <c r="AU168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY168" t="n">
         <v>9</v>
@@ -37332,16 +37332,16 @@
         <v>2.84</v>
       </c>
       <c r="AU169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW169" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX169" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY169" t="n">
         <v>24</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36245,19 +36245,19 @@
         <v>0</v>
       </c>
       <c r="AV164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY164" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ164" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36460,22 +36460,22 @@
         <v>2.88</v>
       </c>
       <c r="AU165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV165" t="n">
         <v>4</v>
       </c>
-      <c r="AV165" t="n">
-        <v>3</v>
-      </c>
       <c r="AW165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX165" t="n">
         <v>4</v>
       </c>
       <c r="AY165" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA165" t="n">
         <v>3</v>
@@ -36684,13 +36684,13 @@
         <v>6</v>
       </c>
       <c r="AW166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX166" t="n">
         <v>5</v>
       </c>
       <c r="AY166" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ166" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36896,16 +36896,16 @@
         <v>2.96</v>
       </c>
       <c r="AU167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV167" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW167" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY167" t="n">
         <v>18</v>
@@ -37114,16 +37114,16 @@
         <v>2.64</v>
       </c>
       <c r="AU168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY168" t="n">
         <v>9</v>
@@ -37332,16 +37332,16 @@
         <v>2.84</v>
       </c>
       <c r="AU169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW169" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX169" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY169" t="n">
         <v>24</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36896,19 +36896,19 @@
         <v>2.96</v>
       </c>
       <c r="AU167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV167" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW167" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AX167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY167" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AZ167" t="n">
         <v>9</v>
@@ -37114,22 +37114,22 @@
         <v>2.64</v>
       </c>
       <c r="AU168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW168" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX168" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY168" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ168" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BA168" t="n">
         <v>4</v>
@@ -37332,22 +37332,22 @@
         <v>2.84</v>
       </c>
       <c r="AU169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW169" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY169" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA169" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36899,13 +36899,13 @@
         <v>5</v>
       </c>
       <c r="AV167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW167" t="n">
         <v>18</v>
       </c>
       <c r="AX167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY167" t="n">
         <v>23</v>
@@ -37332,13 +37332,13 @@
         <v>2.84</v>
       </c>
       <c r="AU169" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV169" t="n">
         <v>2</v>
       </c>
       <c r="AW169" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX169" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -36899,13 +36899,13 @@
         <v>5</v>
       </c>
       <c r="AV167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW167" t="n">
         <v>18</v>
       </c>
       <c r="AX167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY167" t="n">
         <v>23</v>
@@ -37332,13 +37332,13 @@
         <v>2.84</v>
       </c>
       <c r="AU169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV169" t="n">
         <v>2</v>
       </c>
       <c r="AW169" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX169" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.36</v>
@@ -2876,7 +2876,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
         <v>1.67</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.36</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR15" t="n">
         <v>1.73</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR18" t="n">
         <v>2</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR21" t="n">
         <v>1.81</v>
@@ -5271,7 +5271,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.36</v>
@@ -5492,7 +5492,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR23" t="n">
         <v>2.06</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.43</v>
@@ -5928,7 +5928,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR25" t="n">
         <v>1.07</v>
@@ -6143,10 +6143,10 @@
         <v>0.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR26" t="n">
         <v>1.51</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.36</v>
@@ -7454,7 +7454,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR32" t="n">
         <v>0.77</v>
@@ -7669,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR33" t="n">
         <v>1.75</v>
@@ -7890,7 +7890,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR34" t="n">
         <v>1.45</v>
@@ -8323,7 +8323,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.43</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>2.43</v>
@@ -8762,7 +8762,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR38" t="n">
         <v>2.08</v>
@@ -8980,7 +8980,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR39" t="n">
         <v>2</v>
@@ -9195,10 +9195,10 @@
         <v>0.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR40" t="n">
         <v>1.81</v>
@@ -9631,7 +9631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.36</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.43</v>
@@ -10070,7 +10070,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR44" t="n">
         <v>1.58</v>
@@ -10288,7 +10288,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR45" t="n">
         <v>1.64</v>
@@ -10503,7 +10503,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.36</v>
@@ -10724,7 +10724,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR47" t="n">
         <v>0.88</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.07</v>
@@ -11157,10 +11157,10 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR49" t="n">
         <v>1.29</v>
@@ -11375,10 +11375,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR50" t="n">
         <v>1.55</v>
@@ -11596,7 +11596,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR51" t="n">
         <v>1.99</v>
@@ -12029,7 +12029,7 @@
         <v>0.25</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.67</v>
@@ -12247,10 +12247,10 @@
         <v>2.6</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR54" t="n">
         <v>1.75</v>
@@ -12468,7 +12468,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR55" t="n">
         <v>1.17</v>
@@ -12901,10 +12901,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR57" t="n">
         <v>1.5</v>
@@ -13119,10 +13119,10 @@
         <v>1.75</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR58" t="n">
         <v>1.4</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59" t="n">
         <v>2.43</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR60" t="n">
         <v>1.48</v>
@@ -13773,10 +13773,10 @@
         <v>1.25</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR61" t="n">
         <v>1.67</v>
@@ -13991,10 +13991,10 @@
         <v>2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR62" t="n">
         <v>1.6</v>
@@ -14430,7 +14430,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR64" t="n">
         <v>1.93</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.36</v>
@@ -15084,7 +15084,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR67" t="n">
         <v>1.87</v>
@@ -15517,7 +15517,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.67</v>
@@ -16171,10 +16171,10 @@
         <v>2.67</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR72" t="n">
         <v>1.53</v>
@@ -16607,10 +16607,10 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR74" t="n">
         <v>1.46</v>
@@ -16825,10 +16825,10 @@
         <v>0.2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR75" t="n">
         <v>1.41</v>
@@ -17043,7 +17043,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.67</v>
@@ -17261,10 +17261,10 @@
         <v>0.17</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR77" t="n">
         <v>1.38</v>
@@ -17482,7 +17482,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>1.33</v>
@@ -17700,7 +17700,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR79" t="n">
         <v>1.36</v>
@@ -17915,7 +17915,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.36</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.07</v>
@@ -18569,10 +18569,10 @@
         <v>1.86</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR83" t="n">
         <v>1.33</v>
@@ -18787,10 +18787,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR84" t="n">
         <v>1.63</v>
@@ -19005,10 +19005,10 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR85" t="n">
         <v>1.48</v>
@@ -19226,7 +19226,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR86" t="n">
         <v>1.81</v>
@@ -19441,10 +19441,10 @@
         <v>2.43</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR87" t="n">
         <v>1.47</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.36</v>
@@ -20534,7 +20534,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR92" t="n">
         <v>1.21</v>
@@ -20967,10 +20967,10 @@
         <v>0.43</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR94" t="n">
         <v>1.75</v>
@@ -21621,10 +21621,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR97" t="n">
         <v>1.61</v>
@@ -21839,7 +21839,7 @@
         <v>0.86</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.07</v>
@@ -22060,7 +22060,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR99" t="n">
         <v>1.42</v>
@@ -22275,10 +22275,10 @@
         <v>2.13</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR100" t="n">
         <v>1.37</v>
@@ -22493,10 +22493,10 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR101" t="n">
         <v>1.47</v>
@@ -22714,7 +22714,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -22929,7 +22929,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.67</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.43</v>
@@ -23368,7 +23368,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR105" t="n">
         <v>1.64</v>
@@ -23583,7 +23583,7 @@
         <v>2.38</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ106" t="n">
         <v>2.43</v>
@@ -23804,7 +23804,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR107" t="n">
         <v>1.53</v>
@@ -24019,7 +24019,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.36</v>
@@ -24237,7 +24237,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.07</v>
@@ -24458,7 +24458,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR110" t="n">
         <v>1.36</v>
@@ -25109,7 +25109,7 @@
         <v>0.44</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.67</v>
@@ -25330,7 +25330,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR114" t="n">
         <v>1.38</v>
@@ -25763,10 +25763,10 @@
         <v>0.22</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR116" t="n">
         <v>1.37</v>
@@ -25981,10 +25981,10 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR117" t="n">
         <v>1.44</v>
@@ -26199,10 +26199,10 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR118" t="n">
         <v>1.5</v>
@@ -26417,7 +26417,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.07</v>
@@ -26638,7 +26638,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR120" t="n">
         <v>1.51</v>
@@ -26853,7 +26853,7 @@
         <v>2.44</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ121" t="n">
         <v>2.43</v>
@@ -27074,7 +27074,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27289,7 +27289,7 @@
         <v>1.3</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.43</v>
@@ -27507,10 +27507,10 @@
         <v>1.44</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -27946,7 +27946,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR126" t="n">
         <v>1.87</v>
@@ -28161,10 +28161,10 @@
         <v>1.6</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR127" t="n">
         <v>1.69</v>
@@ -28597,10 +28597,10 @@
         <v>1.9</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -28815,7 +28815,7 @@
         <v>2.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130" t="n">
         <v>2.43</v>
@@ -29254,7 +29254,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR132" t="n">
         <v>1.79</v>
@@ -29469,10 +29469,10 @@
         <v>0.27</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR133" t="n">
         <v>1.38</v>
@@ -29687,7 +29687,7 @@
         <v>0.4</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.67</v>
@@ -30123,7 +30123,7 @@
         <v>1.45</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.43</v>
@@ -30344,7 +30344,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR137" t="n">
         <v>1.4</v>
@@ -30562,7 +30562,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR138" t="n">
         <v>1.96</v>
@@ -30777,10 +30777,10 @@
         <v>0.91</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR139" t="n">
         <v>1.61</v>
@@ -30995,7 +30995,7 @@
         <v>1.09</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.07</v>
@@ -31431,10 +31431,10 @@
         <v>1.36</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR142" t="n">
         <v>1.43</v>
@@ -31652,7 +31652,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR143" t="n">
         <v>1.27</v>
@@ -32306,7 +32306,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR146" t="n">
         <v>1.73</v>
@@ -32521,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.07</v>
@@ -32739,7 +32739,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.36</v>
@@ -32960,7 +32960,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR149" t="n">
         <v>1.9</v>
@@ -33393,10 +33393,10 @@
         <v>1.45</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR151" t="n">
         <v>1.56</v>
@@ -33829,7 +33829,7 @@
         <v>1.33</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.36</v>
@@ -34047,10 +34047,10 @@
         <v>0.31</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="AR154" t="n">
         <v>1.64</v>
@@ -34265,10 +34265,10 @@
         <v>1.33</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR155" t="n">
         <v>1.67</v>
@@ -34483,10 +34483,10 @@
         <v>1.54</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR156" t="n">
         <v>1.66</v>
@@ -34704,7 +34704,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR157" t="n">
         <v>1.46</v>
@@ -34919,7 +34919,7 @@
         <v>0.77</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.67</v>
@@ -35140,7 +35140,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR159" t="n">
         <v>1.51</v>
@@ -35573,10 +35573,10 @@
         <v>1.77</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR161" t="n">
         <v>1.41</v>
@@ -35791,7 +35791,7 @@
         <v>2.58</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162" t="n">
         <v>2.43</v>
@@ -36012,7 +36012,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR163" t="n">
         <v>1.71</v>
@@ -36666,7 +36666,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR166" t="n">
         <v>1.4</v>
@@ -37099,7 +37099,7 @@
         <v>1.46</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.36</v>
@@ -37396,6 +37396,1314 @@
       </c>
       <c r="BP169" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7806926</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F170" t="n">
+        <v>29</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+      <c r="N170" t="n">
+        <v>5</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['40', '52', '55']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['66', '75']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X170" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7806927</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F171" t="n">
+        <v>29</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="n">
+        <v>2</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X171" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7806928</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F172" t="n">
+        <v>29</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S172" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X172" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7806930</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F173" t="n">
+        <v>29</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>2</v>
+      </c>
+      <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['66', '87']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S173" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U173" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X173" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7806931</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F174" t="n">
+        <v>29</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" t="n">
+        <v>4</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="n">
+        <v>4</v>
+      </c>
+      <c r="N174" t="n">
+        <v>6</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['24', '41']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['9', '36', '83', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>3</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S174" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U174" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X174" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7806929</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45914.29166666666</v>
+      </c>
+      <c r="F175" t="n">
+        <v>29</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['36', '81']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X175" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/South Korea K League 1_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.53</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.07</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR8" t="n">
         <v>1.25</v>
@@ -2655,7 +2655,7 @@
         <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.07</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.13</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR12" t="n">
         <v>1.67</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.43</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR15" t="n">
         <v>1.73</v>
@@ -4181,7 +4181,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.67</v>
@@ -4402,7 +4402,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>2</v>
@@ -4617,10 +4617,10 @@
         <v>1.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR19" t="n">
         <v>1.33</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.33</v>
@@ -5274,7 +5274,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR23" t="n">
         <v>2.06</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR24" t="n">
         <v>1.69</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.13</v>
@@ -6800,7 +6800,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.36</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR32" t="n">
         <v>0.77</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.13</v>
@@ -7887,10 +7887,10 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR34" t="n">
         <v>1.45</v>
@@ -8326,7 +8326,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR36" t="n">
         <v>1.8</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.53</v>
@@ -8977,7 +8977,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.33</v>
@@ -9198,7 +9198,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR40" t="n">
         <v>1.81</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.43</v>
@@ -9631,7 +9631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.36</v>
@@ -9852,7 +9852,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR43" t="n">
         <v>1.11</v>
@@ -10070,7 +10070,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR44" t="n">
         <v>1.58</v>
@@ -10288,7 +10288,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR45" t="n">
         <v>1.64</v>
@@ -10503,10 +10503,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR46" t="n">
         <v>1.31</v>
@@ -10721,7 +10721,7 @@
         <v>3</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.53</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.07</v>
@@ -11160,7 +11160,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR49" t="n">
         <v>1.29</v>
@@ -11375,10 +11375,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR50" t="n">
         <v>1.55</v>
@@ -11811,10 +11811,10 @@
         <v>0.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR52" t="n">
         <v>1.91</v>
@@ -12465,10 +12465,10 @@
         <v>0.75</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR55" t="n">
         <v>1.17</v>
@@ -12901,10 +12901,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR57" t="n">
         <v>1.5</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ59" t="n">
         <v>2.43</v>
@@ -13558,7 +13558,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR60" t="n">
         <v>1.48</v>
@@ -13773,7 +13773,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.33</v>
@@ -14209,10 +14209,10 @@
         <v>1.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR63" t="n">
         <v>1.32</v>
@@ -14427,10 +14427,10 @@
         <v>1.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR64" t="n">
         <v>1.93</v>
@@ -14645,10 +14645,10 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR65" t="n">
         <v>1.52</v>
@@ -14863,7 +14863,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.07</v>
@@ -15084,7 +15084,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR67" t="n">
         <v>1.87</v>
@@ -15299,7 +15299,7 @@
         <v>2.25</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.43</v>
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.36</v>
@@ -15956,7 +15956,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR71" t="n">
         <v>1.52</v>
@@ -16171,7 +16171,7 @@
         <v>2.67</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.53</v>
@@ -16392,7 +16392,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR73" t="n">
         <v>1.2</v>
@@ -16825,10 +16825,10 @@
         <v>0.2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR75" t="n">
         <v>1.41</v>
@@ -17043,7 +17043,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.67</v>
@@ -17264,7 +17264,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR77" t="n">
         <v>1.38</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.33</v>
@@ -17918,7 +17918,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR80" t="n">
         <v>1.38</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.07</v>
@@ -18790,7 +18790,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR84" t="n">
         <v>1.63</v>
@@ -19005,10 +19005,10 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR85" t="n">
         <v>1.48</v>
@@ -19441,7 +19441,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.53</v>
@@ -20095,7 +20095,7 @@
         <v>0.29</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.67</v>
@@ -20313,10 +20313,10 @@
         <v>1.63</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR91" t="n">
         <v>1.9</v>
@@ -20531,10 +20531,10 @@
         <v>0.29</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR92" t="n">
         <v>1.21</v>
@@ -20752,7 +20752,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR93" t="n">
         <v>1.44</v>
@@ -20967,10 +20967,10 @@
         <v>0.43</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR94" t="n">
         <v>1.75</v>
@@ -21185,7 +21185,7 @@
         <v>1.29</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.36</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.13</v>
@@ -22711,10 +22711,10 @@
         <v>0.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -23147,10 +23147,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR104" t="n">
         <v>1.48</v>
@@ -23368,7 +23368,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR105" t="n">
         <v>1.64</v>
@@ -24237,7 +24237,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.07</v>
@@ -24458,7 +24458,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR110" t="n">
         <v>1.36</v>
@@ -24891,10 +24891,10 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR112" t="n">
         <v>1.72</v>
@@ -25109,7 +25109,7 @@
         <v>0.44</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.67</v>
@@ -25330,7 +25330,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR114" t="n">
         <v>1.38</v>
@@ -25545,10 +25545,10 @@
         <v>1.44</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR115" t="n">
         <v>1.27</v>
@@ -25766,7 +25766,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR116" t="n">
         <v>1.37</v>
@@ -25981,10 +25981,10 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR117" t="n">
         <v>1.44</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.33</v>
@@ -27071,10 +27071,10 @@
         <v>0.9</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR122" t="n">
         <v>1.25</v>
@@ -27289,10 +27289,10 @@
         <v>1.3</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR123" t="n">
         <v>1.63</v>
@@ -27510,7 +27510,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -27725,7 +27725,7 @@
         <v>1.3</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.36</v>
@@ -27943,10 +27943,10 @@
         <v>0.2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR126" t="n">
         <v>1.87</v>
@@ -28161,10 +28161,10 @@
         <v>1.6</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR127" t="n">
         <v>1.69</v>
@@ -28382,7 +28382,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR128" t="n">
         <v>1.57</v>
@@ -28815,7 +28815,7 @@
         <v>2.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ130" t="n">
         <v>2.43</v>
@@ -29251,7 +29251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.13</v>
@@ -29472,7 +29472,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR133" t="n">
         <v>1.38</v>
@@ -29687,7 +29687,7 @@
         <v>0.4</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.67</v>
@@ -29908,7 +29908,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR135" t="n">
         <v>1.5</v>
@@ -30123,10 +30123,10 @@
         <v>1.45</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR136" t="n">
         <v>1.47</v>
@@ -30559,7 +30559,7 @@
         <v>1.82</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.53</v>
@@ -30780,7 +30780,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR139" t="n">
         <v>1.61</v>
@@ -30995,7 +30995,7 @@
         <v>1.09</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.07</v>
@@ -31649,7 +31649,7 @@
         <v>1.42</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.33</v>
@@ -32085,7 +32085,7 @@
         <v>0.64</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.67</v>
@@ -32303,10 +32303,10 @@
         <v>0.25</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR146" t="n">
         <v>1.73</v>
@@ -32521,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.07</v>
@@ -32742,7 +32742,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR148" t="n">
         <v>1.44</v>
@@ -32957,10 +32957,10 @@
         <v>0.83</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR149" t="n">
         <v>1.9</v>
@@ -33175,7 +33175,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.67</v>
@@ -33393,10 +33393,10 @@
         <v>1.45</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR151" t="n">
         <v>1.56</v>
@@ -33614,7 +33614,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR152" t="n">
         <v>1.44</v>
@@ -34047,10 +34047,10 @@
         <v>0.31</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR154" t="n">
         <v>1.64</v>
@@ -34265,7 +34265,7 @@
         <v>1.33</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.13</v>
@@ -35140,7 +35140,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR159" t="n">
         <v>1.51</v>
@@ -35358,7 +35358,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR160" t="n">
         <v>1.43</v>
@@ -35791,7 +35791,7 @@
         <v>2.58</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ162" t="n">
         <v>2.43</v>
@@ -36009,7 +36009,7 @@
         <v>1.23</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.13</v>
@@ -36227,7 +36227,7 @@
         <v>2.38</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.43</v>
@@ -36666,7 +36666,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR166" t="n">
         <v>1.4</v>
@@ -36881,7 +36881,7 @@
         <v>0.92</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.07</v>
@@ -37317,10 +37317,10 @@
         <v>1.46</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR169" t="n">
         <v>1.28</v>
@@ -37753,7 +37753,7 @@
         <v>1.14</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.13</v>
@@ -37971,7 +37971,7 @@
         <v>1.64</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.53</v>
@@ -38192,7 +38192,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR173" t="n">
         <v>1.68</v>
@@ -38407,10 +38407,10 @@
         <v>1.46</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR174" t="n">
         <v>1.72</v>
@@ -38628,7 +38628,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175" t="n">
         <v>1.48</v>
@@ -38704,6 +38704,1314 @@
       </c>
       <c r="BP175" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7806932</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45920.1875</v>
+      </c>
+      <c r="F176" t="n">
+        <v>30</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" t="n">
+        <v>2</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+      <c r="N176" t="n">
+        <v>3</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['39', '45+3']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S176" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U176" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X176" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7806933</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F177" t="n">
+        <v>30</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>2</v>
+      </c>
+      <c r="L177" t="n">
+        <v>3</v>
+      </c>
+      <c r="M177" t="n">
+        <v>2</v>
+      </c>
+      <c r="N177" t="n">
+        <v>5</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['25', '31', '57']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>['72', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U177" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V177" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X177" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7806934</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45921.1875</v>
+      </c>
+      <c r="F178" t="n">
+        <v>30</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U178" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X178" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7806935</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45921.1875</v>
+      </c>
+      <c r="F179" t="n">
+        <v>30</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Suwon</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U179" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V179" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X179" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>7806936</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45921.29166666666</v>
+      </c>
+      <c r="F180" t="n">
+        <v>30</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>['68', '80', '84']</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X180" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>7806937</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>South Korea K League 1</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45921.29166666666</v>
+      </c>
+      <c r="F181" t="n">
+        <v>30</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V181" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X181" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>
